--- a/exports/34003_san-francisco-de-cubaro.xlsx
+++ b/exports/34003_san-francisco-de-cubaro.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M141"/>
+  <dimension ref="A1:M150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -612,22 +612,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>75860528</t>
+          <t>93300732</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AMES</t>
+          <t>ALCANTARA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FABIAN</t>
+          <t>URPI</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ALEXANDER JACK</t>
+          <t>FERNANDO KALEV</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -636,21 +636,21 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>28/07/2002</t>
+          <t>13/03/2023</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -675,22 +675,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>92208423</t>
+          <t>75860528</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ANTAY</t>
+          <t>AMES</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SHANQUETI</t>
+          <t>FABIAN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>THIAGO DAEL</t>
+          <t>ALEXANDER JACK</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -699,16 +699,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>26/01/2021</t>
+          <t>28/07/2002</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -738,35 +738,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>91943957</t>
+          <t>92208423</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ANTONIO</t>
+          <t>ANTAY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>SHANQUETI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MIA YESEL</t>
+          <t>THIAGO DAEL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>23/07/2020</t>
+          <t>26/01/2021</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>23/07/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -801,22 +801,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>94383608</t>
+          <t>91943957</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BARBARON</t>
+          <t>ANTONIO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HUAYLO</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MELODY BRITTANI</t>
+          <t>MIA YESEL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -825,11 +825,11 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>16/09/2025</t>
+          <t>23/07/2020</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>23/07/2025</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -864,27 +864,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>92473990</t>
+          <t>92509986</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BORDA</t>
+          <t>ARAUJO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MARCOS ELIAS</t>
+          <t>CAMILA MIA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -892,7 +892,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>02/08/2021</t>
+          <t>26/08/2021</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -927,27 +927,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>92270512</t>
+          <t>92473990</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CABRERA</t>
+          <t>BORDA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BRIHANA KATALEYA</t>
+          <t>MARCOS ELIAS</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -955,7 +955,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>13/03/2021</t>
+          <t>02/08/2021</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -990,35 +990,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>92479261</t>
+          <t>92270512</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>CABRERA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>JUAN EDOM</t>
+          <t>BRIHANA KATALEYA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>23/07/2020</t>
+          <t>13/03/2021</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>23/07/2025</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1053,35 +1053,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>94573664</t>
+          <t>92479261</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PICHUCA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KIYOMI KASHIRI</t>
+          <t>JUAN EDOM</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>23/07/2020</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>23/07/2025</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1116,7 +1116,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>75272552</t>
+          <t>42898823</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TINEO</t>
+          <t>ASURSA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CARLOS EDUARDO</t>
+          <t>LEVI LEUMIN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>18/04/2004</t>
+          <t>05/01/1985</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>76305763</t>
+          <t>94573664</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>PICHUCA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AIXA FLOR</t>
+          <t>KIYOMI KASHIRI</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1203,21 +1203,21 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>21/08/2003</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1242,22 +1242,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>70934547</t>
+          <t>75272552</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CANDIA</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ALIAGA</t>
+          <t>TINEO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>RINAT BRIAN</t>
+          <t>CARLOS EDUARDO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1266,16 +1266,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>25/06/1992</t>
+          <t>18/04/2004</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1305,40 +1305,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>47406836</t>
+          <t>76305763</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CANO</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MOISES LEOCADIO</t>
+          <t>AIXA FLOR</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>23/10/1992</t>
+          <t>21/08/2003</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>29/05/2024</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1368,40 +1368,40 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>77453508</t>
+          <t>70934547</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t>CANDIA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BENITO</t>
+          <t>ALIAGA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>JAMILETH MISHELLE</t>
+          <t>RINAT BRIAN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>13/12/2011</t>
+          <t>25/06/1992</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>30/07/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,40 +1431,40 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>78629398</t>
+          <t>47406836</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t>CANO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BENITO</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VALERIE AMANDA</t>
+          <t>MOISES LEOCADIO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>21/05/2014</t>
+          <t>23/10/1992</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>30/07/2025</t>
+          <t>29/05/2024</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1494,7 +1494,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>92728182</t>
+          <t>77453508</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SALOME LUZMILA</t>
+          <t>JAMILETH MISHELLE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1518,21 +1518,21 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>27/01/2022</t>
+          <t>13/12/2011</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1557,22 +1557,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>44345957</t>
+          <t>78629398</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CASAS</t>
+          <t>CARBAJAL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ANDAMAYO</t>
+          <t>BENITO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FIORELA</t>
+          <t>VALERIE AMANDA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1581,16 +1581,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20/05/1987</t>
+          <t>21/05/2014</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>04/04/2025</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1620,45 +1620,45 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>71248100</t>
+          <t>92728182</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>CARBAJAL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>BENITO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ROGER ISMAEL</t>
+          <t>SALOME LUZMILA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>11/01/2005</t>
+          <t>27/01/2022</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1683,22 +1683,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>93396934</t>
+          <t>44345957</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CCENTE</t>
+          <t>CASAS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SEBASTIAN</t>
+          <t>ANDAMAYO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>XIMENA MONSERRATH</t>
+          <t>FIORELA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1707,21 +1707,21 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20/05/2023</t>
+          <t>20/05/1987</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>22/07/2024</t>
+          <t>04/04/2025</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1746,40 +1746,40 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>46803939</t>
+          <t>71248100</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CERAS</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CELESTINA MARIBEL</t>
+          <t>ROGER ISMAEL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>17/01/1991</t>
+          <t>11/01/2005</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1809,22 +1809,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>92451942</t>
+          <t>93396934</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>CCENTE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CANO</t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>YATZIRI ZULAY</t>
+          <t>XIMENA MONSERRATH</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1833,11 +1833,11 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>16/07/2021</t>
+          <t>20/05/2023</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>22/07/2024</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1872,22 +1872,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>77020931</t>
+          <t>46803939</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>CERAS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PEÑA</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AYDE SOLEDAD</t>
+          <t>CELESTINA MARIBEL</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1896,11 +1896,11 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>01/01/1996</t>
+          <t>17/01/1991</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>11/02/2025</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1935,7 +1935,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>91987170</t>
+          <t>92451942</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SOLIS</t>
+          <t>CANO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ARANXA YAMILE</t>
+          <t>YATZIRI ZULAY</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1959,11 +1959,11 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>25/08/2020</t>
+          <t>16/07/2021</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1998,22 +1998,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>91878346</t>
+          <t>77020931</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CISNEROS</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ORELLANA</t>
+          <t>PEÑA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ITZAYANA GRISSEL</t>
+          <t>AYDE SOLEDAD</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2022,16 +2022,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>04/06/2020</t>
+          <t>01/01/1996</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>27/06/2025</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2061,40 +2061,40 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>04651057</t>
+          <t>91987170</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>COAPAZA</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MAMANI</t>
+          <t>SOLIS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SAMUEL</t>
+          <t>ARANXA YAMILE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>08/11/1975</t>
+          <t>25/08/2020</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>29/12/2025</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2124,22 +2124,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>21002105</t>
+          <t>91878346</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>CISNEROS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CORDOVA</t>
+          <t>ORELLANA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ENNA</t>
+          <t>ITZAYANA GRISSEL</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2148,16 +2148,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>25/09/1960</t>
+          <t>04/06/2020</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>27/06/2025</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2187,45 +2187,45 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>76264175</t>
+          <t>92509938</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CUTIMANCO</t>
+          <t>CLEMENTE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>QUINTANA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ROCXETT ALTAMIRA</t>
+          <t>ANGEL SMITH</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>21/01/1998</t>
+          <t>26/08/2021</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2250,22 +2250,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>73998397</t>
+          <t>04651057</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DAVILA</t>
+          <t>COAPAZA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SOVERO</t>
+          <t>MAMANI</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>YORDAN EDUARDO</t>
+          <t>SAMUEL</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2274,11 +2274,11 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>07/12/1994</t>
+          <t>08/11/1975</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>29/12/2025</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2313,45 +2313,45 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>92414136</t>
+          <t>21002105</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BERROCAL</t>
+          <t>CORDOVA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ISRAEL SAMUEL</t>
+          <t>ENNA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>21/06/2021</t>
+          <t>25/09/1960</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2376,35 +2376,35 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>75276735</t>
+          <t>76264175</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>CUTIMANCO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CANCHANYA</t>
+          <t>QUINTANA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CARLOS DANIEL</t>
+          <t>ROCXETT ALTAMIRA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>14/04/2004</t>
+          <t>21/01/1998</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2439,45 +2439,45 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09738403</t>
+          <t>94578369</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BALBUENA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AYLE</t>
+          <t>ISABEL LEONOR</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>26/10/1970</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2502,40 +2502,40 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>76550309</t>
+          <t>73998397</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ESCALANTE</t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CURO</t>
+          <t>SOVERO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NAYDA</t>
+          <t>YORDAN EDUARDO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20/06/1999</t>
+          <t>07/12/1994</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2565,22 +2565,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>82017126</t>
+          <t>92414136</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ESCOBAR</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CHANQUETE</t>
+          <t>BERROCAL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>YINO LISANDRO</t>
+          <t>ISRAEL SAMUEL</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2589,11 +2589,11 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>25/07/2022</t>
+          <t>21/06/2021</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2628,35 +2628,35 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>76325298</t>
+          <t>75276735</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ESPINAL</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>CANCHANYA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MARIANELA KELY LEONELA</t>
+          <t>CARLOS DANIEL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>23/07/1998</t>
+          <t>14/04/2004</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2691,22 +2691,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>92269897</t>
+          <t>09738403</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ESQUIVEL</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CAMACLLANQUI</t>
+          <t>BALBUENA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>KEYSON THAYWA</t>
+          <t>AYLE</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2715,21 +2715,21 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>13/03/2021</t>
+          <t>26/10/1970</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2754,40 +2754,40 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>45265629</t>
+          <t>76550309</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EVANGELISTA</t>
+          <t>ESCALANTE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GILVONIO</t>
+          <t>CURO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LEVI ADAN</t>
+          <t>NAYDA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>22/06/1988</t>
+          <t>20/06/1999</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2817,35 +2817,35 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>94286708</t>
+          <t>82017126</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>ESCOBAR</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PAUCARCAJA</t>
+          <t>CHANQUETE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>EMMA</t>
+          <t>YINO LISANDRO</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>25/07/2022</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2880,22 +2880,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>75669769</t>
+          <t>76325298</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GALVEZ</t>
+          <t>ESPINAL</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PROA</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>YENY NOEMI</t>
+          <t>MARIANELA KELY LEONELA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2904,11 +2904,11 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20/10/2002</t>
+          <t>23/07/1998</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>18/02/2025</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2943,45 +2943,45 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>60948568</t>
+          <t>92269897</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>ESQUIVEL</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CENTENO</t>
+          <t>CAMACLLANQUI</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>JACKELYN LAURA</t>
+          <t>KEYSON THAYWA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>28/08/2006</t>
+          <t>13/03/2021</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>03/09/2024</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3006,45 +3006,45 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>92144771</t>
+          <t>45265629</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>EVANGELISTA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MARAVI</t>
+          <t>GILVONIO</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DARA BERENICE</t>
+          <t>LEVI ADAN</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>29/07/2020</t>
+          <t>22/06/1988</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>29/07/2025</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3069,45 +3069,45 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>61444783</t>
+          <t>94286708</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GAVINO</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MAGALLANES</t>
+          <t>PAUCARCAJA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>PAOLO SAMIR</t>
+          <t>EMMA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>01/02/2008</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3132,40 +3132,40 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>80060427</t>
+          <t>75669769</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GILVONIO</t>
+          <t>GALVEZ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LLIHUA</t>
+          <t>PROA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>MAXIMILIANO</t>
+          <t>YENY NOEMI</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>27/11/1978</t>
+          <t>20/10/2002</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>20/08/2024</t>
+          <t>18/02/2025</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3195,22 +3195,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>61256308</t>
+          <t>60948568</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ASPAJO</t>
+          <t>CENTENO</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MARIANA RUBI</t>
+          <t>JACKELYN LAURA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3219,11 +3219,11 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>14/12/2007</t>
+          <t>28/08/2006</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>29/12/2025</t>
+          <t>03/09/2024</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3258,22 +3258,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>70811963</t>
+          <t>92144771</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>QUINTANILLA</t>
+          <t>MARAVI</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MIRELLA CHESSIRA</t>
+          <t>DARA BERENICE</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3282,21 +3282,21 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>07/09/1995</t>
+          <t>29/07/2020</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>11/02/2025</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3321,22 +3321,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>92034282</t>
+          <t>61444783</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GUSMAN</t>
+          <t>GAVINO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>MAGALLANES</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>BERAD JHEBAD</t>
+          <t>PAOLO SAMIR</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3345,16 +3345,16 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>26/09/2020</t>
+          <t>01/02/2008</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3384,45 +3384,45 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>82364968</t>
+          <t>80060427</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>GILVONIO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>LLIHUA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>YANELA</t>
+          <t>MAXIMILIANO</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>08/06/2021</t>
+          <t>27/11/1978</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>20/08/2024</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3447,35 +3447,35 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>74069430</t>
+          <t>61256308</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>ASPAJO</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CRISTHIAN MOISES</t>
+          <t>MARIANA RUBI</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>02/04/1997</t>
+          <t>14/12/2007</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>29/12/2025</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3510,45 +3510,45 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>92118592</t>
+          <t>70811963</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LIMAYMANTA</t>
+          <t>QUINTANILLA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CARLOS SAID</t>
+          <t>MIRELLA CHESSIRA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>19/11/2020</t>
+          <t>07/09/1995</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3573,22 +3573,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>94605928</t>
+          <t>92034282</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HUAMANI</t>
+          <t>GUSMAN</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CULLANCO</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>GHENDY KELLERMAN</t>
+          <t>BERAD JHEBAD</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3597,11 +3597,11 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>26/09/2020</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3636,45 +3636,45 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>71072200</t>
+          <t>82364968</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HUAMANI</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>YULGO</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>IVAN</t>
+          <t>YANELA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>03/02/1991</t>
+          <t>08/06/2021</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3699,22 +3699,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>91950176</t>
+          <t>74069430</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HUAMANTINCO</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>VENTURO</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>DILAN AXEL</t>
+          <t>CRISTHIAN MOISES</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3723,21 +3723,21 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>29/07/2020</t>
+          <t>02/04/1997</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>29/07/2025</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3762,45 +3762,45 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>72120175</t>
+          <t>92118592</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>HUERTA</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HUAYTAN</t>
+          <t>LIMAYMANTA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CATIVEL</t>
+          <t>CARLOS SAID</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>15/12/1994</t>
+          <t>19/11/2020</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3825,35 +3825,35 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>92270389</t>
+          <t>94605928</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JACOBO</t>
+          <t>HUAMANI</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CELESTINO</t>
+          <t>CULLANCO</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>YALESSY JASU</t>
+          <t>GHENDY KELLERMAN</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>13/03/2021</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3888,22 +3888,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>77505517</t>
+          <t>71072200</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JON</t>
+          <t>HUAMANI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>YULGO</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>FRANK ANTONIO</t>
+          <t>IVAN</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3912,16 +3912,16 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>11/04/2006</t>
+          <t>03/02/1991</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>03/09/2025</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3951,22 +3951,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>93942843</t>
+          <t>91950176</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>HUAMANTINCO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SHIAMPA</t>
+          <t>VENTURO</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EYLER</t>
+          <t>DILAN AXEL</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3975,11 +3975,11 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>29/07/2020</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4014,22 +4014,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>91941385</t>
+          <t>72120175</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LAZO</t>
+          <t>HUERTA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GARMA</t>
+          <t>HUAYTAN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ELEN MARIETTDUVITHA</t>
+          <t>CATIVEL</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4038,21 +4038,21 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>23/07/2020</t>
+          <t>15/12/1994</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>23/07/2025</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4077,27 +4077,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>92327614</t>
+          <t>92270389</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LAZO</t>
+          <t>JACOBO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>CELESTINO</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ALHY ISMAEL</t>
+          <t>YALESSY JASU</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>23/04/2021</t>
+          <t>13/03/2021</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4140,22 +4140,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>90647340</t>
+          <t>93942843</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LAZO</t>
+          <t>JOSE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TICLLAS</t>
+          <t>SHIAMPA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>JHOEL JHENDERS</t>
+          <t>EYLER</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4164,11 +4164,11 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>24/02/2018</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4203,45 +4203,45 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10751783</t>
+          <t>91941385</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LEVANO</t>
+          <t>LAZO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>GARMA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>RAUL CARLOS</t>
+          <t>ELEN MARIETTDUVITHA</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>10/02/1978</t>
+          <t>23/07/2020</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>23/07/2025</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4266,22 +4266,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>41680437</t>
+          <t>92327614</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LINO</t>
+          <t>LAZO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ESPIRITU</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>TITO WALTER</t>
+          <t>ALHY ISMAEL</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4290,16 +4290,16 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>06/02/1979</t>
+          <t>23/04/2021</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4329,22 +4329,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>73173972</t>
+          <t>90647340</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LLANCE</t>
+          <t>LAZO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>TICLLAS</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>JHEAN JHONATAN</t>
+          <t>JHOEL JHENDERS</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4353,16 +4353,16 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>13/12/1997</t>
+          <t>24/02/2018</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4392,22 +4392,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>74173759</t>
+          <t>10751783</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MAHUANCA</t>
+          <t>LEVANO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CHIRICENTE</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>HERLY ROEL</t>
+          <t>RAUL CARLOS</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4416,16 +4416,16 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>17/08/2001</t>
+          <t>10/02/1978</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4455,45 +4455,45 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>92464757</t>
+          <t>41680437</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>LINO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SANTA CRUZ</t>
+          <t>ESPIRITU</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>YELITZA</t>
+          <t>TITO WALTER</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>24/06/2021</t>
+          <t>06/02/1979</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4518,35 +4518,35 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>77159359</t>
+          <t>73173972</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MARIN</t>
+          <t>LLANCE</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>MEYLIN MELIZA</t>
+          <t>JHEAN JHONATAN</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>03/03/2006</t>
+          <t>13/12/1997</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4581,22 +4581,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>92420427</t>
+          <t>74173759</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MAYTA</t>
+          <t>MAHUANCA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>CHIRICENTE</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LIAN MOISES</t>
+          <t>HERLY ROEL</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4605,21 +4605,21 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>25/06/2021</t>
+          <t>17/08/2001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4644,22 +4644,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>73198204</t>
+          <t>92464757</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>SANTA CRUZ</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SHELVY CELYM</t>
+          <t>YELITZA</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4668,21 +4668,21 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>30/06/1998</t>
+          <t>24/06/2021</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4707,35 +4707,35 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>73440461</t>
+          <t>77159359</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>MARIN</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BARBARON</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>KINLIMBERG RUSSO</t>
+          <t>MEYLIN MELIZA</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>22/08/2000</t>
+          <t>03/03/2006</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4770,35 +4770,35 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>92152266</t>
+          <t>92420427</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>MAYTA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AMES</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ALESSANDRA VRADESHCA</t>
+          <t>LIAN MOISES</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>13/12/2020</t>
+          <t>25/06/2021</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>29/12/2025</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4833,22 +4833,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>93876723</t>
+          <t>73198204</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MILAN</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SILVIA JIMENA</t>
+          <t>SHELVY CELYM</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4857,16 +4857,16 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>08/06/2019</t>
+          <t>30/06/1998</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>31/07/2024</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4896,35 +4896,35 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>76417696</t>
+          <t>73440461</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MISARAYME</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>QUIÑONEZ</t>
+          <t>BARBARON</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>BRENDA EVELYN</t>
+          <t>KINLIMBERG RUSSO</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>18/11/2002</t>
+          <t>22/08/2000</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4959,40 +4959,40 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>60185820</t>
+          <t>92152266</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MISHICURI</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ALEGRIA</t>
+          <t>AMES</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>RIVALDO</t>
+          <t>ALESSANDRA VRADESHCA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>19/01/2004</t>
+          <t>13/12/2020</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>29/12/2025</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5022,35 +5022,35 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>90695093</t>
+          <t>93876723</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MORI</t>
+          <t>MILAN</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PAQUI</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ISAI IGNACIO</t>
+          <t>SILVIA JIMENA</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>17/03/2018</t>
+          <t>08/06/2019</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>31/07/2024</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5085,40 +5085,40 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>91912222</t>
+          <t>76417696</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>MISARAYME</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SORIA</t>
+          <t>QUIÑONEZ</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>MILMER</t>
+          <t>BRENDA EVELYN</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>30/06/2020</t>
+          <t>18/11/2002</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5148,22 +5148,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>91660823</t>
+          <t>60185820</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>MISHICURI</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>ALEGRIA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>GHAEL IYAN ALDEMAR</t>
+          <t>RIVALDO</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5172,16 +5172,16 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>19/01/2004</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5211,22 +5211,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>77659342</t>
+          <t>90695093</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>MORI</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CHANQUETE</t>
+          <t>PAQUI</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>JUNIOR PEPE</t>
+          <t>ISAI IGNACIO</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5235,16 +5235,16 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>17/09/2003</t>
+          <t>17/03/2018</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5274,40 +5274,40 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>72302311</t>
+          <t>91912222</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MAÑAHUIRI</t>
+          <t>SORIA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>JUANA</t>
+          <t>MILMER</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>24/05/1995</t>
+          <t>30/06/2020</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>02/05/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5337,22 +5337,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>92441541</t>
+          <t>91660823</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NINAHUANCA</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>OSCANOA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LUIS MIGUEL</t>
+          <t>GHAEL IYAN ALDEMAR</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5361,11 +5361,11 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>09/07/2021</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5400,22 +5400,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>47617480</t>
+          <t>77659342</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>OCHICUA</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BETTER</t>
+          <t>CHANQUETE</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>JHYN LUIS</t>
+          <t>JUNIOR PEPE</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5424,16 +5424,16 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>24/10/1991</t>
+          <t>17/09/2003</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5463,40 +5463,40 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>75957326</t>
+          <t>72302311</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TINTA</t>
+          <t>MAÑAHUIRI</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>OSWALDO JAHIRO</t>
+          <t>JUANA</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>08/05/1999</t>
+          <t>24/05/1995</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>02/05/2025</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5526,22 +5526,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>48345322</t>
+          <t>92441541</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ORELLANA</t>
+          <t>NINAHUANCA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MENESES</t>
+          <t>OSCANOA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>JAIME</t>
+          <t>LUIS MIGUEL</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5550,16 +5550,16 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>25/07/1993</t>
+          <t>09/07/2021</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5589,22 +5589,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>73071269</t>
+          <t>47617480</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ORELLANA</t>
+          <t>OCHICUA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SUCUITANA</t>
+          <t>BETTER</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LUIS ALFREDO</t>
+          <t>JHYN LUIS</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5613,11 +5613,11 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>28/09/1996</t>
+          <t>24/10/1991</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5652,40 +5652,40 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>74841035</t>
+          <t>75957326</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ORTEGA</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>TINTA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>TATYANA AFRODITA</t>
+          <t>OSWALDO JAHIRO</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>01/08/1994</t>
+          <t>08/05/1999</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5715,22 +5715,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>63418421</t>
+          <t>48345322</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>ORELLANA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>MENESES</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>SEBASTIAN</t>
+          <t>JAIME</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5739,16 +5739,16 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>08/05/2015</t>
+          <t>25/07/1993</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>03/09/2024</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5778,40 +5778,40 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>92061264</t>
+          <t>73071269</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>OTAROLA</t>
+          <t>ORELLANA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>SUCUITANA</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LUIS ALFREDO</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>14/10/2020</t>
+          <t>28/09/1996</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5841,22 +5841,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>81832366</t>
+          <t>92509001</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PABLO</t>
+          <t>OROSCO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SANTONINO</t>
+          <t>JANAMPA</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ELI JOEL</t>
+          <t>NOE IMER</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5865,11 +5865,11 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>02/11/2020</t>
+          <t>26/08/2021</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5904,40 +5904,40 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>73863007</t>
+          <t>74841035</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PAICO</t>
+          <t>ORTEGA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ALEXANDRO</t>
+          <t>TATYANA AFRODITA</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>06/05/2002</t>
+          <t>01/08/1994</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5967,35 +5967,35 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>94477359</t>
+          <t>63418421</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PAITAN</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GASPAR</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>MIA YAMILETH</t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>08/05/2015</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>03/09/2024</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6030,22 +6030,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>92118196</t>
+          <t>92061264</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PALMA</t>
+          <t>OTAROLA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>REATEGUI</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ALESSIA DANAE</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>19/11/2020</t>
+          <t>14/10/2020</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6093,40 +6093,40 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>74690615</t>
+          <t>81832366</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PAMPAS</t>
+          <t>PABLO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>SANTONINO</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ROXANA</t>
+          <t>ELI JOEL</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>22/02/1998</t>
+          <t>02/11/2020</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6156,40 +6156,40 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>21011537</t>
+          <t>73863007</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PARDO</t>
+          <t>PAICO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ANTONIO</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>CLAUDIA</t>
+          <t>ALEXANDRO</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20/03/1961</t>
+          <t>06/05/2002</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6219,45 +6219,45 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>76728774</t>
+          <t>94477359</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PARIACHI</t>
+          <t>PAITAN</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CUÑIVO</t>
+          <t>GASPAR</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>GESER RONALD</t>
+          <t>MIA YAMILETH</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>15/03/1996</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6282,27 +6282,27 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>91855829</t>
+          <t>92118196</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PARIACHI</t>
+          <t>PALMA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>LAZARO</t>
+          <t>REATEGUI</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VALENTIN JUNIOR</t>
+          <t>ALESSIA DANAE</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>16/05/2020</t>
+          <t>19/11/2020</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6345,40 +6345,40 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>46350087</t>
+          <t>74690615</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>PAMPAS</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LISMAN CARLOS</t>
+          <t>ROXANA</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>31/05/1990</t>
+          <t>22/02/1998</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>29/12/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6408,22 +6408,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>91949940</t>
+          <t>92510301</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>PAQUI</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SOBRINO</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>KATLEYA ZOE</t>
+          <t>CARMENCITA YASURI</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6432,11 +6432,11 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>29/07/2020</t>
+          <t>26/08/2021</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>29/07/2025</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6471,45 +6471,45 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>91996112</t>
+          <t>21011537</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>PARDO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>UMPIQUIRI</t>
+          <t>ANTONIO</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>JACK TEDDY</t>
+          <t>CLAUDIA</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>29/07/2020</t>
+          <t>20/03/1961</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>29/07/2025</t>
+          <t>19/08/2025</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6534,40 +6534,40 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>92061695</t>
+          <t>76728774</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>QUINTANA</t>
+          <t>PARIACHI</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>UNSIHUAY</t>
+          <t>CUÑIVO</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>BRIANA ARLETH</t>
+          <t>GESER RONALD</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>14/10/2020</t>
+          <t>15/03/1996</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6597,22 +6597,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>94647520</t>
+          <t>91855829</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>PARIACHI</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ARCA</t>
+          <t>LAZARO</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ZAEL SAMIR</t>
+          <t>VALENTIN JUNIOR</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6621,11 +6621,11 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2020</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6660,40 +6660,40 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>78554669</t>
+          <t>92483488</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ORIHUELA</t>
+          <t>ARCO</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>BRIANA DANIELA</t>
+          <t>GAEL PATRICK</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>06/04/2014</t>
+          <t>08/08/2021</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6723,22 +6723,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>75285464</t>
+          <t>46350087</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MAÑUICO</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>JHON ANTONY</t>
+          <t>LISMAN CARLOS</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6747,16 +6747,16 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>01/04/1998</t>
+          <t>31/05/1990</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>29/12/2025</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6786,27 +6786,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>92104257</t>
+          <t>91949940</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>RASHUAMAN</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FABIAN</t>
+          <t>SOBRINO</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>UZIEL DANIEL</t>
+          <t>KATLEYA ZOE</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>10/11/2020</t>
+          <t>29/07/2020</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6849,35 +6849,35 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>92474195</t>
+          <t>91996112</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>RAYMUNDO</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>UMPIQUIRI</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ALESSIA ZOE</t>
+          <t>JACK TEDDY</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>02/08/2021</t>
+          <t>29/07/2020</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6912,22 +6912,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>92460080</t>
+          <t>90653705</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>REMUZGO</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>PANCHO</t>
+          <t>VILLALVA</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>MARY CARMEN</t>
+          <t>DANNA DALUSKA</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6936,11 +6936,11 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>22/07/2021</t>
+          <t>27/02/2018</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6975,22 +6975,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>78548631</t>
+          <t>92061695</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>QUINTANA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>DELGADO</t>
+          <t>UNSIHUAY</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>JOHANA CLAUDINA</t>
+          <t>BRIANA ARLETH</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6999,16 +6999,16 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>12/01/2003</t>
+          <t>14/10/2020</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7038,35 +7038,35 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>92459078</t>
+          <t>94647520</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>ARCA</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>BRIANA KELSI</t>
+          <t>ZAEL SAMIR</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>21/07/2021</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7101,40 +7101,40 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>60786771</t>
+          <t>78554669</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>RODRIGO</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>ORIHUELA</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>BRUNO BRAYAN</t>
+          <t>BRIANA DANIELA</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>07/06/2006</t>
+          <t>06/04/2014</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>18/06/2024</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7164,22 +7164,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>41786424</t>
+          <t>92510667</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ARANDA</t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>HELMER LEONIDAS</t>
+          <t>LIAN JAIRO</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7188,21 +7188,21 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>04/05/1982</t>
+          <t>26/08/2021</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>10/07/2024</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7227,22 +7227,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>72016831</t>
+          <t>75285464</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BENDEZU</t>
+          <t>MAÑUICO</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>CESAR SAMUEL</t>
+          <t>JHON ANTONY</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7251,11 +7251,11 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>31/12/1999</t>
+          <t>01/04/1998</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7290,35 +7290,35 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>92419021</t>
+          <t>92104257</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ROMANI</t>
+          <t>RASHUAMAN</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MENDIOLAZA</t>
+          <t>FABIAN</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ZOE ISABEL</t>
+          <t>UZIEL DANIEL</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>24/06/2021</t>
+          <t>10/11/2020</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7353,45 +7353,45 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>48121806</t>
+          <t>92474195</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t>RAYMUNDO</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>JOHN MIJAEL</t>
+          <t>ALESSIA ZOE</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>18/02/1988</t>
+          <t>02/08/2021</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7416,22 +7416,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>94438245</t>
+          <t>92460080</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ROSPIGLIOSI</t>
+          <t>REMUZGO</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MAYHUANTI</t>
+          <t>PANCHO</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>DANNAE ARIANA</t>
+          <t>MARY CARMEN</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7440,11 +7440,11 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>22/07/2021</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7479,22 +7479,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>92269981</t>
+          <t>78548631</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SAENZ</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>PAUCAR</t>
+          <t>DELGADO</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NAIRA ANALI</t>
+          <t>JOHANA CLAUDINA</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7503,21 +7503,21 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>13/03/2021</t>
+          <t>12/01/2003</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7542,22 +7542,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>92459642</t>
+          <t>92459078</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SALAS</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>LARA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ASHLEY JHOSABET</t>
+          <t>BRIANA KELSI</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7605,22 +7605,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>47943181</t>
+          <t>60786771</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SALDAÑA</t>
+          <t>RODRIGO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>JHOA CHRISTIAN</t>
+          <t>BRUNO BRAYAN</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7629,16 +7629,16 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>02/08/1993</t>
+          <t>07/06/2006</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>18/06/2024</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7668,22 +7668,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>92259920</t>
+          <t>41786424</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BARRETO</t>
+          <t>ARANDA</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>GAEL JAIME</t>
+          <t>HELMER LEONIDAS</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7692,16 +7692,16 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>06/03/2021</t>
+          <t>04/05/1982</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>10/07/2024</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7731,45 +7731,45 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>91950188</t>
+          <t>72016831</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SHUMPATI</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>BENDEZU</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>JHASMIN HEYRA</t>
+          <t>CESAR SAMUEL</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>29/07/2020</t>
+          <t>31/12/1999</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>29/07/2025</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7794,27 +7794,27 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>92383249</t>
+          <t>92419021</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SIERRA</t>
+          <t>ROMANI</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>PAMPAS</t>
+          <t>MENDIOLAZA</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>JAIRO SAMIR</t>
+          <t>ZOE ISABEL</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>30/05/2021</t>
+          <t>24/06/2021</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7857,45 +7857,45 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>94303923</t>
+          <t>48121806</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SOLIS</t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>KARELIZ SARAY</t>
+          <t>JOHN MIJAEL</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>05/07/2025</t>
+          <t>18/02/1988</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7920,35 +7920,35 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>92267094</t>
+          <t>94438245</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>ROSPIGLIOSI</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>MAYHUANTI</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>DYLAN PERCY</t>
+          <t>DANNAE ARIANA</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>11/03/2021</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7983,22 +7983,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>81757730</t>
+          <t>92269981</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SUAZO</t>
+          <t>SAENZ</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>PAUCAR</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>CAMILA DOMINGA</t>
+          <t>NAIRA ANALI</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8007,11 +8007,11 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>23/07/2020</t>
+          <t>13/03/2021</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>23/07/2025</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8046,22 +8046,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>92211363</t>
+          <t>92459642</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SURICHAQUI</t>
+          <t>SALAS</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>GAUGA</t>
+          <t>LARA</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ESTRELLA SALOME</t>
+          <t>ASHLEY JHOSABET</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>28/01/2021</t>
+          <t>21/07/2021</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8109,22 +8109,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>92394996</t>
+          <t>92509183</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TAIPE</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SEDANO</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>HANSEL YENSEI</t>
+          <t>CAMILO STELLO ENRRIQUE</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>08/06/2021</t>
+          <t>26/08/2021</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8172,40 +8172,40 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>74974093</t>
+          <t>47943181</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TAQUIRE</t>
+          <t>SALDAÑA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>EMILY YASSDELY</t>
+          <t>JHOA CHRISTIAN</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>04/05/1999</t>
+          <t>02/08/1993</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8235,27 +8235,27 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>92457610</t>
+          <t>92259920</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TEJADA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CHIRISENTE</t>
+          <t>BARRETO</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NIRLET YELIXA</t>
+          <t>GAEL JAIME</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>21/07/2021</t>
+          <t>06/03/2021</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8298,22 +8298,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>92417110</t>
+          <t>91950188</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TELLO</t>
+          <t>SHUMPATI</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>KENDRA EDURNE</t>
+          <t>JHASMIN HEYRA</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8322,11 +8322,11 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>22/06/2021</t>
+          <t>29/07/2020</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8361,40 +8361,40 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>73780756</t>
+          <t>92383249</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>SIERRA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>TANGOA</t>
+          <t>PAMPAS</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>MARIANELA</t>
+          <t>JAIRO SAMIR</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>18/03/2004</t>
+          <t>30/05/2021</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8424,22 +8424,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>78532814</t>
+          <t>94303923</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>SOLIS</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MALPARTIDA</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ROSE KIARA</t>
+          <t>KARELIZ SARAY</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8448,21 +8448,21 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>03/04/2014</t>
+          <t>05/07/2025</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>11/02/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8487,22 +8487,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>92572906</t>
+          <t>92267094</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>PINEDO</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ARTURO ACXEL</t>
+          <t>DYLAN PERCY</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>23/01/2021</t>
+          <t>11/03/2021</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8550,22 +8550,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>44863817</t>
+          <t>81757730</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TOVAR</t>
+          <t>SUAZO</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CHIHUAN</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>SOLEDAD</t>
+          <t>CAMILA DOMINGA</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8574,16 +8574,16 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>21/08/1982</t>
+          <t>23/07/2020</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>06/07/2013</t>
+          <t>23/07/2025</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8613,35 +8613,35 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>92118073</t>
+          <t>92211363</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>UNCHUPAICO</t>
+          <t>SURICHAQUI</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>GAUGA</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>GAEL SEBASTIAN</t>
+          <t>ESTRELLA SALOME</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>19/11/2020</t>
+          <t>28/01/2021</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8676,45 +8676,45 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>77483796</t>
+          <t>92394996</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>VALERO</t>
+          <t>TAIPE</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>TOVAR</t>
+          <t>SEDANO</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>JAQUI YADITH</t>
+          <t>HANSEL YENSEI</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>06/03/2004</t>
+          <t>08/06/2021</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>VULNERABILIDAD SANITARIA - DISCAPACIDAD SEVERA (DS Nº 002-2020-SA)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>06/07/2013</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8739,45 +8739,45 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>62207706</t>
+          <t>74974093</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>VALERO</t>
+          <t>TAQUIRE</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TOVAR</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>EDINSON</t>
+          <t>EMILY YASSDELY</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>11/08/2010</t>
+          <t>04/05/1999</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>14/03/2019</t>
+          <t>11/02/2026</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8802,35 +8802,35 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>92118606</t>
+          <t>92457610</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>VALERO</t>
+          <t>TEJADA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>CHIRISENTE</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>PATRICK SMITTH</t>
+          <t>NIRLET YELIXA</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>19/11/2020</t>
+          <t>21/07/2021</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8865,27 +8865,27 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>92182206</t>
+          <t>92417110</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>TELLO</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>PUENTE</t>
+          <t>VELIZ</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>DARWIN ANTONIO</t>
+          <t>KENDRA EDURNE</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -8893,7 +8893,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>05/01/2021</t>
+          <t>22/06/2021</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8928,22 +8928,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>75279953</t>
+          <t>73780756</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SALAS</t>
+          <t>TANGOA</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>MARA KRISTEL</t>
+          <t>MARIANELA</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8952,11 +8952,11 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>04/10/2005</t>
+          <t>18/03/2004</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8991,22 +8991,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>41172450</t>
+          <t>78532814</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>VELASQUEZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>MALPARTIDA</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>CARMEN ROSA</t>
+          <t>ROSE KIARA</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -9015,16 +9015,16 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>02/12/1981</t>
+          <t>03/04/2014</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9054,22 +9054,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>92421803</t>
+          <t>92572906</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>BERNARDO</t>
+          <t>PINEDO</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>PEDRO ARTURO</t>
+          <t>ARTURO ACXEL</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>25/06/2021</t>
+          <t>23/01/2021</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -9117,22 +9117,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>92299052</t>
+          <t>44863817</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>VERA</t>
+          <t>TOVAR</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>CHIHUAN</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>KATALLEA ASUMI</t>
+          <t>SOLEDAD</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -9141,21 +9141,21 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>03/04/2021</t>
+          <t>21/08/1982</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>06/07/2013</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -9180,45 +9180,45 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>72877156</t>
+          <t>92118073</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>YUPANQUI</t>
+          <t>UNCHUPAICO</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>HUALLULLO</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>GLEYDI DANEY</t>
+          <t>GAEL SEBASTIAN</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20/05/1993</t>
+          <t>19/11/2020</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -9243,63 +9243,630 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
+          <t>77483796</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>VALERO</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>TOVAR</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>JAQUI YADITH</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>22</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>06/03/2004</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>3.JOVEN</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>VULNERABILIDAD SANITARIA - DISCAPACIDAD SEVERA (DS Nº 002-2020-SA)</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>06/07/2013</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M141" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>62207706</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>VALERO</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>TOVAR</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>EDINSON</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>16</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>11/08/2010</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>2.ADOLESCENTE</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>14/03/2019</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M142" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>92118606</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>VALERO</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>VASQUEZ</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>PATRICK SMITTH</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>6</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>19/11/2020</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>19/11/2025</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M143" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>92182206</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>VASQUEZ</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>PUENTE</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>DARWIN ANTONIO</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>5</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>05/01/2021</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>13/01/2026</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M144" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>75279953</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>VASQUEZ</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>SALAS</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>MARA KRISTEL</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>21</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>04/10/2005</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>3.JOVEN</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>06/01/2025</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M145" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>41172450</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>APOLINARIO</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>CARMEN ROSA</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>45</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>02/12/1981</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>4.ADULTO</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>05/04/2025</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M146" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>92421803</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>VELIZ</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>BERNARDO</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>PEDRO ARTURO</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>5</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>25/06/2021</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M147" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>92299052</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>VERA</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>KATALLEA ASUMI</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>5</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>03/04/2021</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M148" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>40405181</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>YAURI</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ORELLANA</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>EVELYN KATYUSCA</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>46</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>15/01/1980</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>4.ADULTO</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M149" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
           <t>81932339</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>ZACARIAS</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="C150" t="inlineStr">
         <is>
           <t>ASENCIO</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D150" t="inlineStr">
         <is>
           <t>CELESTE RUTH</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="E150" t="inlineStr">
         <is>
           <t>Femenino</t>
         </is>
       </c>
-      <c r="F141" t="n">
+      <c r="F150" t="n">
         <v>5</v>
       </c>
-      <c r="G141" t="inlineStr">
+      <c r="G150" t="inlineStr">
         <is>
           <t>22/06/2021</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
+      <c r="H150" t="inlineStr">
         <is>
           <t>1.NIÑO</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
+      <c r="I150" t="inlineStr">
         <is>
           <t>AFILIACION PPDD</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>MAZAMARI</t>
-        </is>
-      </c>
-      <c r="M141" t="n">
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M150" t="n">
         <v>120604</v>
       </c>
     </row>

--- a/exports/34003_san-francisco-de-cubaro.xlsx
+++ b/exports/34003_san-francisco-de-cubaro.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M150"/>
+  <dimension ref="A1:M141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -612,22 +612,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>93300732</t>
+          <t>75860528</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ALCANTARA</t>
+          <t>AMES</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>URPI</t>
+          <t>FABIAN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FERNANDO KALEV</t>
+          <t>ALEXANDER JACK</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -636,21 +636,21 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>13/03/2023</t>
+          <t>28/07/2002</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -675,22 +675,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>75860528</t>
+          <t>92208423</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AMES</t>
+          <t>ANTAY</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FABIAN</t>
+          <t>SHANQUETI</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ALEXANDER JACK</t>
+          <t>THIAGO DAEL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -699,16 +699,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>28/07/2002</t>
+          <t>26/01/2021</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -738,35 +738,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>92208423</t>
+          <t>91943957</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ANTAY</t>
+          <t>ANTONIO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SHANQUETI</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>THIAGO DAEL</t>
+          <t>MIA YESEL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>26/01/2021</t>
+          <t>23/07/2020</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>23/07/2025</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -801,22 +801,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>91943957</t>
+          <t>94383608</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ANTONIO</t>
+          <t>BARBARON</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>HUAYLO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MIA YESEL</t>
+          <t>MELODY BRITTANI</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -825,11 +825,11 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>23/07/2020</t>
+          <t>16/09/2025</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>23/07/2025</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -864,27 +864,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>92509986</t>
+          <t>92473990</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ARAUJO</t>
+          <t>BORDA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CAMILA MIA</t>
+          <t>MARCOS ELIAS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -892,7 +892,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>26/08/2021</t>
+          <t>02/08/2021</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -927,27 +927,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>92473990</t>
+          <t>92270512</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BORDA</t>
+          <t>CABRERA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MARCOS ELIAS</t>
+          <t>BRIHANA KATALEYA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -955,7 +955,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>02/08/2021</t>
+          <t>13/03/2021</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -990,35 +990,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>92270512</t>
+          <t>92479261</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CABRERA</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BRIHANA KATALEYA</t>
+          <t>JUAN EDOM</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>13/03/2021</t>
+          <t>23/07/2020</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>23/07/2025</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1053,35 +1053,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>92479261</t>
+          <t>94573664</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>PICHUCA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>JUAN EDOM</t>
+          <t>KIYOMI KASHIRI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>23/07/2020</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>23/07/2025</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1116,7 +1116,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>42898823</t>
+          <t>75272552</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ASURSA</t>
+          <t>TINEO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LEVI LEUMIN</t>
+          <t>CARLOS EDUARDO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>05/01/1985</t>
+          <t>18/04/2004</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>94573664</t>
+          <t>76305763</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PICHUCA</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KIYOMI KASHIRI</t>
+          <t>AIXA FLOR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1203,21 +1203,21 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>21/08/2003</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1242,22 +1242,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>75272552</t>
+          <t>70934547</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>CANDIA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TINEO</t>
+          <t>ALIAGA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CARLOS EDUARDO</t>
+          <t>RINAT BRIAN</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1266,16 +1266,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>18/04/2004</t>
+          <t>25/06/1992</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1305,40 +1305,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>76305763</t>
+          <t>47406836</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>CANO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AIXA FLOR</t>
+          <t>MOISES LEOCADIO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>21/08/2003</t>
+          <t>23/10/1992</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>29/05/2024</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1368,40 +1368,40 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>70934547</t>
+          <t>77453508</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CANDIA</t>
+          <t>CARBAJAL</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ALIAGA</t>
+          <t>BENITO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>RINAT BRIAN</t>
+          <t>JAMILETH MISHELLE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>25/06/1992</t>
+          <t>13/12/2011</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,40 +1431,40 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>47406836</t>
+          <t>78629398</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CANO</t>
+          <t>CARBAJAL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>BENITO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MOISES LEOCADIO</t>
+          <t>VALERIE AMANDA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>23/10/1992</t>
+          <t>21/05/2014</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>29/05/2024</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1494,7 +1494,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>77453508</t>
+          <t>92728182</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>JAMILETH MISHELLE</t>
+          <t>SALOME LUZMILA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1518,21 +1518,21 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>13/12/2011</t>
+          <t>27/01/2022</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1557,22 +1557,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>78629398</t>
+          <t>44345957</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t>CASAS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BENITO</t>
+          <t>ANDAMAYO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VALERIE AMANDA</t>
+          <t>FIORELA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1581,16 +1581,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>21/05/2014</t>
+          <t>20/05/1987</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>30/07/2025</t>
+          <t>04/04/2025</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1620,45 +1620,45 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>92728182</t>
+          <t>71248100</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BENITO</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SALOME LUZMILA</t>
+          <t>ROGER ISMAEL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>27/01/2022</t>
+          <t>11/01/2005</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>30/07/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1683,22 +1683,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>44345957</t>
+          <t>93396934</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CASAS</t>
+          <t>CCENTE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ANDAMAYO</t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FIORELA</t>
+          <t>XIMENA MONSERRATH</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1707,21 +1707,21 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20/05/1987</t>
+          <t>20/05/2023</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>04/04/2025</t>
+          <t>22/07/2024</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1746,40 +1746,40 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>71248100</t>
+          <t>46803939</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>CERAS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ROGER ISMAEL</t>
+          <t>CELESTINA MARIBEL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>11/01/2005</t>
+          <t>17/01/1991</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1809,22 +1809,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>93396934</t>
+          <t>92451942</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CCENTE</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SEBASTIAN</t>
+          <t>CANO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>XIMENA MONSERRATH</t>
+          <t>YATZIRI ZULAY</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1833,11 +1833,11 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20/05/2023</t>
+          <t>16/07/2021</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>22/07/2024</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1872,22 +1872,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>46803939</t>
+          <t>77020931</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CERAS</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>PEÑA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CELESTINA MARIBEL</t>
+          <t>AYDE SOLEDAD</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1896,11 +1896,11 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>17/01/1991</t>
+          <t>01/01/1996</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1935,7 +1935,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>92451942</t>
+          <t>91987170</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CANO</t>
+          <t>SOLIS</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>YATZIRI ZULAY</t>
+          <t>ARANXA YAMILE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1959,11 +1959,11 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>16/07/2021</t>
+          <t>25/08/2020</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1998,22 +1998,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>77020931</t>
+          <t>91878346</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>CISNEROS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PEÑA</t>
+          <t>ORELLANA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>AYDE SOLEDAD</t>
+          <t>ITZAYANA GRISSEL</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2022,16 +2022,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>01/01/1996</t>
+          <t>04/06/2020</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>11/02/2025</t>
+          <t>27/06/2025</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2061,40 +2061,40 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>91987170</t>
+          <t>04651057</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>COAPAZA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SOLIS</t>
+          <t>MAMANI</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ARANXA YAMILE</t>
+          <t>SAMUEL</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>25/08/2020</t>
+          <t>08/11/1975</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>29/12/2025</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2124,22 +2124,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>91878346</t>
+          <t>21002105</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CISNEROS</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ORELLANA</t>
+          <t>CORDOVA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ITZAYANA GRISSEL</t>
+          <t>ENNA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2148,16 +2148,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>04/06/2020</t>
+          <t>25/09/1960</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>27/06/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2187,45 +2187,45 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>92509938</t>
+          <t>76264175</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CLEMENTE</t>
+          <t>CUTIMANCO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>QUINTANA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ANGEL SMITH</t>
+          <t>ROCXETT ALTAMIRA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>26/08/2021</t>
+          <t>21/01/1998</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2250,22 +2250,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>04651057</t>
+          <t>73998397</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>COAPAZA</t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MAMANI</t>
+          <t>SOVERO</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SAMUEL</t>
+          <t>YORDAN EDUARDO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2274,11 +2274,11 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>08/11/1975</t>
+          <t>07/12/1994</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>29/12/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2313,45 +2313,45 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>21002105</t>
+          <t>92414136</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CORDOVA</t>
+          <t>BERROCAL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ENNA</t>
+          <t>ISRAEL SAMUEL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>25/09/1960</t>
+          <t>21/06/2021</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2376,35 +2376,35 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>76264175</t>
+          <t>75276735</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CUTIMANCO</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>QUINTANA</t>
+          <t>CANCHANYA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ROCXETT ALTAMIRA</t>
+          <t>CARLOS DANIEL</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>21/01/1998</t>
+          <t>14/04/2004</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2439,45 +2439,45 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>94578369</t>
+          <t>09738403</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DAVILA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>BALBUENA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ISABEL LEONOR</t>
+          <t>AYLE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>26/10/1970</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2502,40 +2502,40 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>73998397</t>
+          <t>76550309</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DAVILA</t>
+          <t>ESCALANTE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SOVERO</t>
+          <t>CURO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>YORDAN EDUARDO</t>
+          <t>NAYDA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>07/12/1994</t>
+          <t>20/06/1999</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2565,22 +2565,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>92414136</t>
+          <t>82017126</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>ESCOBAR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BERROCAL</t>
+          <t>CHANQUETE</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ISRAEL SAMUEL</t>
+          <t>YINO LISANDRO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2589,11 +2589,11 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>21/06/2021</t>
+          <t>25/07/2022</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2628,35 +2628,35 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>75276735</t>
+          <t>76325298</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>ESPINAL</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CANCHANYA</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CARLOS DANIEL</t>
+          <t>MARIANELA KELY LEONELA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>14/04/2004</t>
+          <t>23/07/1998</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2691,22 +2691,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09738403</t>
+          <t>92269897</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>ESQUIVEL</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BALBUENA</t>
+          <t>CAMACLLANQUI</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AYLE</t>
+          <t>KEYSON THAYWA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2715,21 +2715,21 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>26/10/1970</t>
+          <t>13/03/2021</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2754,40 +2754,40 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>76550309</t>
+          <t>45265629</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ESCALANTE</t>
+          <t>EVANGELISTA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CURO</t>
+          <t>GILVONIO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NAYDA</t>
+          <t>LEVI ADAN</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20/06/1999</t>
+          <t>22/06/1988</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2817,35 +2817,35 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>82017126</t>
+          <t>94286708</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ESCOBAR</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CHANQUETE</t>
+          <t>PAUCARCAJA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>YINO LISANDRO</t>
+          <t>EMMA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>25/07/2022</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2880,22 +2880,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>76325298</t>
+          <t>75669769</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ESPINAL</t>
+          <t>GALVEZ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>PROA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>MARIANELA KELY LEONELA</t>
+          <t>YENY NOEMI</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2904,11 +2904,11 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>23/07/1998</t>
+          <t>20/10/2002</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>18/02/2025</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2943,45 +2943,45 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>92269897</t>
+          <t>60948568</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ESQUIVEL</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CAMACLLANQUI</t>
+          <t>CENTENO</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>KEYSON THAYWA</t>
+          <t>JACKELYN LAURA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>13/03/2021</t>
+          <t>28/08/2006</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>03/09/2024</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3006,45 +3006,45 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>45265629</t>
+          <t>92144771</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EVANGELISTA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GILVONIO</t>
+          <t>MARAVI</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LEVI ADAN</t>
+          <t>DARA BERENICE</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>22/06/1988</t>
+          <t>29/07/2020</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3069,45 +3069,45 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>94286708</t>
+          <t>61444783</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>GAVINO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PAUCARCAJA</t>
+          <t>MAGALLANES</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EMMA</t>
+          <t>PAOLO SAMIR</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>01/02/2008</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3132,40 +3132,40 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>75669769</t>
+          <t>80060427</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GALVEZ</t>
+          <t>GILVONIO</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PROA</t>
+          <t>LLIHUA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>YENY NOEMI</t>
+          <t>MAXIMILIANO</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20/10/2002</t>
+          <t>27/11/1978</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>18/02/2025</t>
+          <t>20/08/2024</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3195,22 +3195,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>60948568</t>
+          <t>61256308</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CENTENO</t>
+          <t>ASPAJO</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>JACKELYN LAURA</t>
+          <t>MARIANA RUBI</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3219,11 +3219,11 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>28/08/2006</t>
+          <t>14/12/2007</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>03/09/2024</t>
+          <t>29/12/2025</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3258,22 +3258,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>92144771</t>
+          <t>70811963</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MARAVI</t>
+          <t>QUINTANILLA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DARA BERENICE</t>
+          <t>MIRELLA CHESSIRA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3282,21 +3282,21 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>29/07/2020</t>
+          <t>07/09/1995</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>29/07/2025</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3321,22 +3321,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>61444783</t>
+          <t>92034282</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GAVINO</t>
+          <t>GUSMAN</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MAGALLANES</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>PAOLO SAMIR</t>
+          <t>BERAD JHEBAD</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3345,16 +3345,16 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>01/02/2008</t>
+          <t>26/09/2020</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3384,45 +3384,45 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>80060427</t>
+          <t>82364968</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GILVONIO</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LLIHUA</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>MAXIMILIANO</t>
+          <t>YANELA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>27/11/1978</t>
+          <t>08/06/2021</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>20/08/2024</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3447,35 +3447,35 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>61256308</t>
+          <t>74069430</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ASPAJO</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>MARIANA RUBI</t>
+          <t>CRISTHIAN MOISES</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>14/12/2007</t>
+          <t>02/04/1997</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>29/12/2025</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3510,45 +3510,45 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>70811963</t>
+          <t>92118592</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>QUINTANILLA</t>
+          <t>LIMAYMANTA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>MIRELLA CHESSIRA</t>
+          <t>CARLOS SAID</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>07/09/1995</t>
+          <t>19/11/2020</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>11/02/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3573,22 +3573,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>92034282</t>
+          <t>94605928</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GUSMAN</t>
+          <t>HUAMANI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>CULLANCO</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>BERAD JHEBAD</t>
+          <t>GHENDY KELLERMAN</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3597,11 +3597,11 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>26/09/2020</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3636,45 +3636,45 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>82364968</t>
+          <t>71072200</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>HUAMANI</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>YULGO</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>YANELA</t>
+          <t>IVAN</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>08/06/2021</t>
+          <t>03/02/1991</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3699,22 +3699,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>74069430</t>
+          <t>91950176</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>HUAMANTINCO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>VENTURO</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CRISTHIAN MOISES</t>
+          <t>DILAN AXEL</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3723,21 +3723,21 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>02/04/1997</t>
+          <t>29/07/2020</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3762,45 +3762,45 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>92118592</t>
+          <t>72120175</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>HUERTA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LIMAYMANTA</t>
+          <t>HUAYTAN</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CARLOS SAID</t>
+          <t>CATIVEL</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>19/11/2020</t>
+          <t>15/12/1994</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3825,35 +3825,35 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>94605928</t>
+          <t>92270389</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>HUAMANI</t>
+          <t>JACOBO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CULLANCO</t>
+          <t>CELESTINO</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>GHENDY KELLERMAN</t>
+          <t>YALESSY JASU</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/03/2021</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3888,22 +3888,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>71072200</t>
+          <t>77505517</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HUAMANI</t>
+          <t>JON</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>YULGO</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>IVAN</t>
+          <t>FRANK ANTONIO</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3912,16 +3912,16 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>03/02/1991</t>
+          <t>11/04/2006</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>03/09/2025</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3951,22 +3951,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>91950176</t>
+          <t>93942843</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HUAMANTINCO</t>
+          <t>JOSE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>VENTURO</t>
+          <t>SHIAMPA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DILAN AXEL</t>
+          <t>EYLER</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3975,11 +3975,11 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>29/07/2020</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>29/07/2025</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4014,22 +4014,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>72120175</t>
+          <t>91941385</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>HUERTA</t>
+          <t>LAZO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>HUAYTAN</t>
+          <t>GARMA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CATIVEL</t>
+          <t>ELEN MARIETTDUVITHA</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4038,21 +4038,21 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>15/12/1994</t>
+          <t>23/07/2020</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>23/07/2025</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4077,27 +4077,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>92270389</t>
+          <t>92327614</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JACOBO</t>
+          <t>LAZO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CELESTINO</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>YALESSY JASU</t>
+          <t>ALHY ISMAEL</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>13/03/2021</t>
+          <t>23/04/2021</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4140,22 +4140,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>93942843</t>
+          <t>90647340</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>LAZO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SHIAMPA</t>
+          <t>TICLLAS</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>EYLER</t>
+          <t>JHOEL JHENDERS</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4164,11 +4164,11 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>24/02/2018</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4203,45 +4203,45 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>91941385</t>
+          <t>10751783</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LAZO</t>
+          <t>LEVANO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GARMA</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ELEN MARIETTDUVITHA</t>
+          <t>RAUL CARLOS</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>23/07/2020</t>
+          <t>10/02/1978</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>23/07/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4266,22 +4266,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>92327614</t>
+          <t>41680437</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LAZO</t>
+          <t>LINO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>ESPIRITU</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ALHY ISMAEL</t>
+          <t>TITO WALTER</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4290,16 +4290,16 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>23/04/2021</t>
+          <t>06/02/1979</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4329,22 +4329,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>90647340</t>
+          <t>73173972</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LAZO</t>
+          <t>LLANCE</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TICLLAS</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>JHOEL JHENDERS</t>
+          <t>JHEAN JHONATAN</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4353,16 +4353,16 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>24/02/2018</t>
+          <t>13/12/1997</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4392,22 +4392,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10751783</t>
+          <t>74173759</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LEVANO</t>
+          <t>MAHUANCA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>CHIRICENTE</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>RAUL CARLOS</t>
+          <t>HERLY ROEL</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4416,16 +4416,16 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>10/02/1978</t>
+          <t>17/08/2001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4455,45 +4455,45 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>41680437</t>
+          <t>92464757</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LINO</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ESPIRITU</t>
+          <t>SANTA CRUZ</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>TITO WALTER</t>
+          <t>YELITZA</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>06/02/1979</t>
+          <t>24/06/2021</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4518,35 +4518,35 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>73173972</t>
+          <t>77159359</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LLANCE</t>
+          <t>MARIN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>JHEAN JHONATAN</t>
+          <t>MEYLIN MELIZA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>13/12/1997</t>
+          <t>03/03/2006</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4581,22 +4581,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>74173759</t>
+          <t>92420427</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MAHUANCA</t>
+          <t>MAYTA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CHIRICENTE</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>HERLY ROEL</t>
+          <t>LIAN MOISES</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4605,21 +4605,21 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>17/08/2001</t>
+          <t>25/06/2021</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4644,22 +4644,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>92464757</t>
+          <t>73198204</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SANTA CRUZ</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>YELITZA</t>
+          <t>SHELVY CELYM</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4668,21 +4668,21 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>24/06/2021</t>
+          <t>30/06/1998</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4707,35 +4707,35 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>77159359</t>
+          <t>73440461</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MARIN</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>BARBARON</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>MEYLIN MELIZA</t>
+          <t>KINLIMBERG RUSSO</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>03/03/2006</t>
+          <t>22/08/2000</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4770,35 +4770,35 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>92420427</t>
+          <t>92152266</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MAYTA</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>AMES</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LIAN MOISES</t>
+          <t>ALESSANDRA VRADESHCA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>25/06/2021</t>
+          <t>13/12/2020</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/12/2025</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4833,22 +4833,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>73198204</t>
+          <t>93876723</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>MILAN</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SHELVY CELYM</t>
+          <t>SILVIA JIMENA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4857,16 +4857,16 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>30/06/1998</t>
+          <t>08/06/2019</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>31/07/2024</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4896,35 +4896,35 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>73440461</t>
+          <t>76417696</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>MISARAYME</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BARBARON</t>
+          <t>QUIÑONEZ</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>KINLIMBERG RUSSO</t>
+          <t>BRENDA EVELYN</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>22/08/2000</t>
+          <t>18/11/2002</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4959,40 +4959,40 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>92152266</t>
+          <t>60185820</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>MISHICURI</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AMES</t>
+          <t>ALEGRIA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ALESSANDRA VRADESHCA</t>
+          <t>RIVALDO</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>13/12/2020</t>
+          <t>19/01/2004</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>29/12/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5022,35 +5022,35 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>93876723</t>
+          <t>90695093</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MILAN</t>
+          <t>MORI</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>PAQUI</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SILVIA JIMENA</t>
+          <t>ISAI IGNACIO</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>08/06/2019</t>
+          <t>17/03/2018</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>31/07/2024</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5085,40 +5085,40 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>76417696</t>
+          <t>91912222</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MISARAYME</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>QUIÑONEZ</t>
+          <t>SORIA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>BRENDA EVELYN</t>
+          <t>MILMER</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>18/11/2002</t>
+          <t>30/06/2020</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5148,22 +5148,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>60185820</t>
+          <t>91660823</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MISHICURI</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ALEGRIA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>RIVALDO</t>
+          <t>GHAEL IYAN ALDEMAR</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5172,16 +5172,16 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>19/01/2004</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5211,22 +5211,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>90695093</t>
+          <t>77659342</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MORI</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PAQUI</t>
+          <t>CHANQUETE</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ISAI IGNACIO</t>
+          <t>JUNIOR PEPE</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5235,16 +5235,16 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>17/03/2018</t>
+          <t>17/09/2003</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5274,40 +5274,40 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>91912222</t>
+          <t>72302311</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SORIA</t>
+          <t>MAÑAHUIRI</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>MILMER</t>
+          <t>JUANA</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>30/06/2020</t>
+          <t>24/05/1995</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>02/05/2025</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5337,22 +5337,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>91660823</t>
+          <t>92441541</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>NINAHUANCA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>OSCANOA</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>GHAEL IYAN ALDEMAR</t>
+          <t>LUIS MIGUEL</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5361,11 +5361,11 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>09/07/2021</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5400,22 +5400,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>77659342</t>
+          <t>47617480</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>OCHICUA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CHANQUETE</t>
+          <t>BETTER</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>JUNIOR PEPE</t>
+          <t>JHYN LUIS</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5424,16 +5424,16 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>17/09/2003</t>
+          <t>24/10/1991</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5463,40 +5463,40 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>72302311</t>
+          <t>75957326</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MAÑAHUIRI</t>
+          <t>TINTA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>JUANA</t>
+          <t>OSWALDO JAHIRO</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>24/05/1995</t>
+          <t>08/05/1999</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>02/05/2025</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5526,22 +5526,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>92441541</t>
+          <t>48345322</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NINAHUANCA</t>
+          <t>ORELLANA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>OSCANOA</t>
+          <t>MENESES</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LUIS MIGUEL</t>
+          <t>JAIME</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5550,16 +5550,16 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>09/07/2021</t>
+          <t>25/07/1993</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5589,22 +5589,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>47617480</t>
+          <t>73071269</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>OCHICUA</t>
+          <t>ORELLANA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BETTER</t>
+          <t>SUCUITANA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>JHYN LUIS</t>
+          <t>LUIS ALFREDO</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5613,11 +5613,11 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>24/10/1991</t>
+          <t>28/09/1996</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5652,40 +5652,40 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>75957326</t>
+          <t>74841035</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>ORTEGA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TINTA</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>OSWALDO JAHIRO</t>
+          <t>TATYANA AFRODITA</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>08/05/1999</t>
+          <t>01/08/1994</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5715,22 +5715,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>48345322</t>
+          <t>63418421</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ORELLANA</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MENESES</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>JAIME</t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5739,16 +5739,16 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>25/07/1993</t>
+          <t>08/05/2015</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>03/09/2024</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5778,40 +5778,40 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>73071269</t>
+          <t>92061264</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ORELLANA</t>
+          <t>OTAROLA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SUCUITANA</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LUIS ALFREDO</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>28/09/1996</t>
+          <t>14/10/2020</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5841,22 +5841,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>92509001</t>
+          <t>81832366</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>OROSCO</t>
+          <t>PABLO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>JANAMPA</t>
+          <t>SANTONINO</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NOE IMER</t>
+          <t>ELI JOEL</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5865,11 +5865,11 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>26/08/2021</t>
+          <t>02/11/2020</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5904,40 +5904,40 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>74841035</t>
+          <t>73863007</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ORTEGA</t>
+          <t>PAICO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>TATYANA AFRODITA</t>
+          <t>ALEXANDRO</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>01/08/1994</t>
+          <t>06/05/2002</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5967,35 +5967,35 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>63418421</t>
+          <t>94477359</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>PAITAN</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>GASPAR</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SEBASTIAN</t>
+          <t>MIA YAMILETH</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>08/05/2015</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>03/09/2024</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6030,22 +6030,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>92061264</t>
+          <t>92118196</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>OTAROLA</t>
+          <t>PALMA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>REATEGUI</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ALESSIA DANAE</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>14/10/2020</t>
+          <t>19/11/2020</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6093,40 +6093,40 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>81832366</t>
+          <t>74690615</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PABLO</t>
+          <t>PAMPAS</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SANTONINO</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ELI JOEL</t>
+          <t>ROXANA</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>02/11/2020</t>
+          <t>22/02/1998</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6156,40 +6156,40 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>73863007</t>
+          <t>21011537</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PAICO</t>
+          <t>PARDO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>ANTONIO</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ALEXANDRO</t>
+          <t>CLAUDIA</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>06/05/2002</t>
+          <t>20/03/1961</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>19/08/2025</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6219,45 +6219,45 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>94477359</t>
+          <t>76728774</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PAITAN</t>
+          <t>PARIACHI</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GASPAR</t>
+          <t>CUÑIVO</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>MIA YAMILETH</t>
+          <t>GESER RONALD</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>15/03/1996</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6282,27 +6282,27 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>92118196</t>
+          <t>91855829</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PALMA</t>
+          <t>PARIACHI</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>REATEGUI</t>
+          <t>LAZARO</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ALESSIA DANAE</t>
+          <t>VALENTIN JUNIOR</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>19/11/2020</t>
+          <t>16/05/2020</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6345,40 +6345,40 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>74690615</t>
+          <t>46350087</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PAMPAS</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ROXANA</t>
+          <t>LISMAN CARLOS</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>22/02/1998</t>
+          <t>31/05/1990</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>29/12/2025</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6408,22 +6408,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>92510301</t>
+          <t>91949940</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PAQUI</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>SOBRINO</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>CARMENCITA YASURI</t>
+          <t>KATLEYA ZOE</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6432,11 +6432,11 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>26/08/2021</t>
+          <t>29/07/2020</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6471,45 +6471,45 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>21011537</t>
+          <t>91996112</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PARDO</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ANTONIO</t>
+          <t>UMPIQUIRI</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>CLAUDIA</t>
+          <t>JACK TEDDY</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20/03/1961</t>
+          <t>29/07/2020</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6534,40 +6534,40 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>76728774</t>
+          <t>92061695</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PARIACHI</t>
+          <t>QUINTANA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CUÑIVO</t>
+          <t>UNSIHUAY</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>GESER RONALD</t>
+          <t>BRIANA ARLETH</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>15/03/1996</t>
+          <t>14/10/2020</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6597,22 +6597,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>91855829</t>
+          <t>94647520</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PARIACHI</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>LAZARO</t>
+          <t>ARCA</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VALENTIN JUNIOR</t>
+          <t>ZAEL SAMIR</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6621,11 +6621,11 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>16/05/2020</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6660,40 +6660,40 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>92483488</t>
+          <t>78554669</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ARCO</t>
+          <t>ORIHUELA</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>GAEL PATRICK</t>
+          <t>BRIANA DANIELA</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>08/08/2021</t>
+          <t>06/04/2014</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6723,22 +6723,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>46350087</t>
+          <t>75285464</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>MAÑUICO</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LISMAN CARLOS</t>
+          <t>JHON ANTONY</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6747,16 +6747,16 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>31/05/1990</t>
+          <t>01/04/1998</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>29/12/2025</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6786,27 +6786,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>91949940</t>
+          <t>92104257</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>RASHUAMAN</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SOBRINO</t>
+          <t>FABIAN</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>KATLEYA ZOE</t>
+          <t>UZIEL DANIEL</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>29/07/2020</t>
+          <t>10/11/2020</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>29/07/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6849,35 +6849,35 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>91996112</t>
+          <t>92474195</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>RAYMUNDO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>UMPIQUIRI</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>JACK TEDDY</t>
+          <t>ALESSIA ZOE</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>29/07/2020</t>
+          <t>02/08/2021</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>29/07/2025</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6912,22 +6912,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>90653705</t>
+          <t>92460080</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>REMUZGO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>VILLALVA</t>
+          <t>PANCHO</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>DANNA DALUSKA</t>
+          <t>MARY CARMEN</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6936,11 +6936,11 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>27/02/2018</t>
+          <t>22/07/2021</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6975,22 +6975,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>92061695</t>
+          <t>78548631</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>QUINTANA</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>UNSIHUAY</t>
+          <t>DELGADO</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>BRIANA ARLETH</t>
+          <t>JOHANA CLAUDINA</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6999,16 +6999,16 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>14/10/2020</t>
+          <t>12/01/2003</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7038,35 +7038,35 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>94647520</t>
+          <t>92459078</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ARCA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ZAEL SAMIR</t>
+          <t>BRIANA KELSI</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>21/07/2021</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7101,40 +7101,40 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>78554669</t>
+          <t>60786771</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>RODRIGO</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ORIHUELA</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>BRIANA DANIELA</t>
+          <t>BRUNO BRAYAN</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>06/04/2014</t>
+          <t>07/06/2006</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>18/06/2024</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7164,22 +7164,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>92510667</t>
+          <t>41786424</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t>ARANDA</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LIAN JAIRO</t>
+          <t>HELMER LEONIDAS</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7188,21 +7188,21 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>26/08/2021</t>
+          <t>04/05/1982</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>10/07/2024</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7227,22 +7227,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>75285464</t>
+          <t>72016831</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MAÑUICO</t>
+          <t>BENDEZU</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>JHON ANTONY</t>
+          <t>CESAR SAMUEL</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7251,11 +7251,11 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>01/04/1998</t>
+          <t>31/12/1999</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7290,35 +7290,35 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>92104257</t>
+          <t>92419021</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>RASHUAMAN</t>
+          <t>ROMANI</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FABIAN</t>
+          <t>MENDIOLAZA</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>UZIEL DANIEL</t>
+          <t>ZOE ISABEL</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>10/11/2020</t>
+          <t>24/06/2021</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7353,45 +7353,45 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>92474195</t>
+          <t>48121806</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>RAYMUNDO</t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ALESSIA ZOE</t>
+          <t>JOHN MIJAEL</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>02/08/2021</t>
+          <t>18/02/1988</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7416,22 +7416,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>92460080</t>
+          <t>94438245</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>REMUZGO</t>
+          <t>ROSPIGLIOSI</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PANCHO</t>
+          <t>MAYHUANTI</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>MARY CARMEN</t>
+          <t>DANNAE ARIANA</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7440,11 +7440,11 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>22/07/2021</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7479,22 +7479,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>78548631</t>
+          <t>92269981</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>SAENZ</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>DELGADO</t>
+          <t>PAUCAR</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>JOHANA CLAUDINA</t>
+          <t>NAIRA ANALI</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7503,21 +7503,21 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>12/01/2003</t>
+          <t>13/03/2021</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7542,22 +7542,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>92459078</t>
+          <t>92459642</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>SALAS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>LARA</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>BRIANA KELSI</t>
+          <t>ASHLEY JHOSABET</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7605,22 +7605,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>60786771</t>
+          <t>47943181</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>RODRIGO</t>
+          <t>SALDAÑA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>BRUNO BRAYAN</t>
+          <t>JHOA CHRISTIAN</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7629,16 +7629,16 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>07/06/2006</t>
+          <t>02/08/1993</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>18/06/2024</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7668,22 +7668,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>41786424</t>
+          <t>92259920</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ARANDA</t>
+          <t>BARRETO</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>HELMER LEONIDAS</t>
+          <t>GAEL JAIME</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7692,16 +7692,16 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>04/05/1982</t>
+          <t>06/03/2021</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>10/07/2024</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7731,45 +7731,45 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>72016831</t>
+          <t>91950188</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>SHUMPATI</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BENDEZU</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>CESAR SAMUEL</t>
+          <t>JHASMIN HEYRA</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>31/12/1999</t>
+          <t>29/07/2020</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7794,27 +7794,27 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>92419021</t>
+          <t>92383249</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ROMANI</t>
+          <t>SIERRA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>MENDIOLAZA</t>
+          <t>PAMPAS</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ZOE ISABEL</t>
+          <t>JAIRO SAMIR</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>24/06/2021</t>
+          <t>30/05/2021</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7857,45 +7857,45 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>48121806</t>
+          <t>94303923</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t>SOLIS</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>JOHN MIJAEL</t>
+          <t>KARELIZ SARAY</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>18/02/1988</t>
+          <t>05/07/2025</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7920,35 +7920,35 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>94438245</t>
+          <t>92267094</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ROSPIGLIOSI</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MAYHUANTI</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>DANNAE ARIANA</t>
+          <t>DYLAN PERCY</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>11/03/2021</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7983,22 +7983,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>92269981</t>
+          <t>81757730</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SAENZ</t>
+          <t>SUAZO</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>PAUCAR</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NAIRA ANALI</t>
+          <t>CAMILA DOMINGA</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8007,11 +8007,11 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>13/03/2021</t>
+          <t>23/07/2020</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>23/07/2025</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8046,22 +8046,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>92459642</t>
+          <t>92211363</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SALAS</t>
+          <t>SURICHAQUI</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>LARA</t>
+          <t>GAUGA</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ASHLEY JHOSABET</t>
+          <t>ESTRELLA SALOME</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>21/07/2021</t>
+          <t>28/01/2021</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8109,22 +8109,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>92509183</t>
+          <t>92394996</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>TAIPE</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>SEDANO</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>CAMILO STELLO ENRRIQUE</t>
+          <t>HANSEL YENSEI</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>26/08/2021</t>
+          <t>08/06/2021</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8172,40 +8172,40 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>47943181</t>
+          <t>74974093</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SALDAÑA</t>
+          <t>TAQUIRE</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>JHOA CHRISTIAN</t>
+          <t>EMILY YASSDELY</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>02/08/1993</t>
+          <t>04/05/1999</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>11/02/2026</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8235,27 +8235,27 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>92259920</t>
+          <t>92457610</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>TEJADA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>BARRETO</t>
+          <t>CHIRISENTE</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>GAEL JAIME</t>
+          <t>NIRLET YELIXA</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>06/03/2021</t>
+          <t>21/07/2021</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8298,22 +8298,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>91950188</t>
+          <t>92417110</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SHUMPATI</t>
+          <t>TELLO</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>VELIZ</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>JHASMIN HEYRA</t>
+          <t>KENDRA EDURNE</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8322,11 +8322,11 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>29/07/2020</t>
+          <t>22/06/2021</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>29/07/2025</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8361,40 +8361,40 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>92383249</t>
+          <t>73780756</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SIERRA</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>PAMPAS</t>
+          <t>TANGOA</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>JAIRO SAMIR</t>
+          <t>MARIANELA</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>30/05/2021</t>
+          <t>18/03/2004</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8424,22 +8424,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>94303923</t>
+          <t>78532814</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SOLIS</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>MALPARTIDA</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>KARELIZ SARAY</t>
+          <t>ROSE KIARA</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8448,21 +8448,21 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>05/07/2025</t>
+          <t>03/04/2014</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8487,22 +8487,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>92267094</t>
+          <t>92572906</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>PINEDO</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>DYLAN PERCY</t>
+          <t>ARTURO ACXEL</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>11/03/2021</t>
+          <t>23/01/2021</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8550,22 +8550,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>81757730</t>
+          <t>44863817</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SUAZO</t>
+          <t>TOVAR</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>CHIHUAN</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>CAMILA DOMINGA</t>
+          <t>SOLEDAD</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8574,16 +8574,16 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>23/07/2020</t>
+          <t>21/08/1982</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>23/07/2025</t>
+          <t>06/07/2013</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8613,35 +8613,35 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>92211363</t>
+          <t>92118073</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SURICHAQUI</t>
+          <t>UNCHUPAICO</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>GAUGA</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ESTRELLA SALOME</t>
+          <t>GAEL SEBASTIAN</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>28/01/2021</t>
+          <t>19/11/2020</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8676,45 +8676,45 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>92394996</t>
+          <t>77483796</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>TAIPE</t>
+          <t>VALERO</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SEDANO</t>
+          <t>TOVAR</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>HANSEL YENSEI</t>
+          <t>JAQUI YADITH</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>08/06/2021</t>
+          <t>06/03/2004</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>VULNERABILIDAD SANITARIA - DISCAPACIDAD SEVERA (DS Nº 002-2020-SA)</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>06/07/2013</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8739,45 +8739,45 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>74974093</t>
+          <t>62207706</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TAQUIRE</t>
+          <t>VALERO</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>TOVAR</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>EMILY YASSDELY</t>
+          <t>EDINSON</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>04/05/1999</t>
+          <t>11/08/2010</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>14/03/2019</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8802,35 +8802,35 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>92457610</t>
+          <t>92118606</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>TEJADA</t>
+          <t>VALERO</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CHIRISENTE</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NIRLET YELIXA</t>
+          <t>PATRICK SMITTH</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>21/07/2021</t>
+          <t>19/11/2020</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8865,27 +8865,27 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>92417110</t>
+          <t>92182206</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>TELLO</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>PUENTE</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>KENDRA EDURNE</t>
+          <t>DARWIN ANTONIO</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -8893,7 +8893,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>22/06/2021</t>
+          <t>05/01/2021</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8928,22 +8928,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>73780756</t>
+          <t>75279953</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>TANGOA</t>
+          <t>SALAS</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>MARIANELA</t>
+          <t>MARA KRISTEL</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8952,11 +8952,11 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>18/03/2004</t>
+          <t>04/10/2005</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8991,22 +8991,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>78532814</t>
+          <t>41172450</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>VELASQUEZ</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>MALPARTIDA</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ROSE KIARA</t>
+          <t>CARMEN ROSA</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -9015,16 +9015,16 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>03/04/2014</t>
+          <t>02/12/1981</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>11/02/2025</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9054,22 +9054,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>92572906</t>
+          <t>92421803</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>VELIZ</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>PINEDO</t>
+          <t>BERNARDO</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>ARTURO ACXEL</t>
+          <t>PEDRO ARTURO</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>23/01/2021</t>
+          <t>25/06/2021</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -9117,22 +9117,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>44863817</t>
+          <t>92299052</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>TOVAR</t>
+          <t>VERA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>CHIHUAN</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>SOLEDAD</t>
+          <t>KATALLEA ASUMI</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -9141,21 +9141,21 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>21/08/1982</t>
+          <t>03/04/2021</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>06/07/2013</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -9180,45 +9180,45 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>92118073</t>
+          <t>72877156</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>UNCHUPAICO</t>
+          <t>YUPANQUI</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>HUALLULLO</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>GAEL SEBASTIAN</t>
+          <t>GLEYDI DANEY</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>19/11/2020</t>
+          <t>20/05/1993</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -9243,22 +9243,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>77483796</t>
+          <t>81932339</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>VALERO</t>
+          <t>ZACARIAS</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>TOVAR</t>
+          <t>ASENCIO</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>JAQUI YADITH</t>
+          <t>CELESTE RUTH</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9267,21 +9267,21 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>06/03/2004</t>
+          <t>22/06/2021</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>VULNERABILIDAD SANITARIA - DISCAPACIDAD SEVERA (DS Nº 002-2020-SA)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>06/07/2013</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -9300,573 +9300,6 @@
         </is>
       </c>
       <c r="M141" t="n">
-        <v>120604</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>62207706</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>VALERO</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>TOVAR</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>EDINSON</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F142" t="n">
-        <v>16</v>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>11/08/2010</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>2.ADOLESCENTE</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>14/03/2019</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>MAZAMARI</t>
-        </is>
-      </c>
-      <c r="M142" t="n">
-        <v>120604</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>92118606</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>VALERO</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>VASQUEZ</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>PATRICK SMITTH</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F143" t="n">
-        <v>6</v>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>19/11/2020</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>19/11/2025</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>MAZAMARI</t>
-        </is>
-      </c>
-      <c r="M143" t="n">
-        <v>120604</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>92182206</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>VASQUEZ</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>PUENTE</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>DARWIN ANTONIO</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F144" t="n">
-        <v>5</v>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>05/01/2021</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>13/01/2026</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>MAZAMARI</t>
-        </is>
-      </c>
-      <c r="M144" t="n">
-        <v>120604</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>75279953</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>VASQUEZ</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>SALAS</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>MARA KRISTEL</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="F145" t="n">
-        <v>21</v>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>04/10/2005</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>3.JOVEN</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>06/01/2025</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>MAZAMARI</t>
-        </is>
-      </c>
-      <c r="M145" t="n">
-        <v>120604</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>41172450</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>VELASQUEZ</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>APOLINARIO</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>CARMEN ROSA</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="F146" t="n">
-        <v>45</v>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>02/12/1981</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>4.ADULTO</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>05/04/2025</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>MAZAMARI</t>
-        </is>
-      </c>
-      <c r="M146" t="n">
-        <v>120604</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>92421803</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>VELIZ</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>BERNARDO</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>PEDRO ARTURO</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F147" t="n">
-        <v>5</v>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>25/06/2021</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>MAZAMARI</t>
-        </is>
-      </c>
-      <c r="M147" t="n">
-        <v>120604</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>92299052</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>VERA</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>FERNANDEZ</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>KATALLEA ASUMI</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="F148" t="n">
-        <v>5</v>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>03/04/2021</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>MAZAMARI</t>
-        </is>
-      </c>
-      <c r="M148" t="n">
-        <v>120604</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>40405181</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>YAURI</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>ORELLANA</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>EVELYN KATYUSCA</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="F149" t="n">
-        <v>46</v>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>15/01/1980</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>4.ADULTO</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>24/08/2026</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>MAZAMARI</t>
-        </is>
-      </c>
-      <c r="M149" t="n">
-        <v>120604</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>81932339</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>ZACARIAS</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>ASENCIO</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>CELESTE RUTH</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="F150" t="n">
-        <v>5</v>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>22/06/2021</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>MAZAMARI</t>
-        </is>
-      </c>
-      <c r="M150" t="n">
         <v>120604</v>
       </c>
     </row>

--- a/exports/34003_san-francisco-de-cubaro.xlsx
+++ b/exports/34003_san-francisco-de-cubaro.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M141"/>
+  <dimension ref="A1:M151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -612,22 +612,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>75860528</t>
+          <t>93300732</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AMES</t>
+          <t>ALCANTARA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FABIAN</t>
+          <t>URPI</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ALEXANDER JACK</t>
+          <t>FERNANDO KALEV</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -636,21 +636,21 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>28/07/2002</t>
+          <t>13/03/2023</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -675,22 +675,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>92208423</t>
+          <t>75860528</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ANTAY</t>
+          <t>AMES</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SHANQUETI</t>
+          <t>FABIAN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>THIAGO DAEL</t>
+          <t>ALEXANDER JACK</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -699,16 +699,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>26/01/2021</t>
+          <t>28/07/2002</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -738,35 +738,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>91943957</t>
+          <t>92208423</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ANTONIO</t>
+          <t>ANTAY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>SHANQUETI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MIA YESEL</t>
+          <t>THIAGO DAEL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>23/07/2020</t>
+          <t>26/01/2021</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>23/07/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -801,22 +801,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>94383608</t>
+          <t>91943957</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BARBARON</t>
+          <t>ANTONIO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HUAYLO</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MELODY BRITTANI</t>
+          <t>MIA YESEL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -825,11 +825,11 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>16/09/2025</t>
+          <t>23/07/2020</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>23/07/2025</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -864,27 +864,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>92473990</t>
+          <t>92509986</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BORDA</t>
+          <t>ARAUJO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MARCOS ELIAS</t>
+          <t>CAMILA MIA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -892,7 +892,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>02/08/2021</t>
+          <t>26/08/2021</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -927,27 +927,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>92270512</t>
+          <t>92473990</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CABRERA</t>
+          <t>BORDA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BRIHANA KATALEYA</t>
+          <t>MARCOS ELIAS</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -955,7 +955,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>13/03/2021</t>
+          <t>02/08/2021</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -990,35 +990,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>92479261</t>
+          <t>92270512</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>CABRERA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>JUAN EDOM</t>
+          <t>BRIHANA KATALEYA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>23/07/2020</t>
+          <t>13/03/2021</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>23/07/2025</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1053,35 +1053,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>94573664</t>
+          <t>92479261</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PICHUCA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KIYOMI KASHIRI</t>
+          <t>JUAN EDOM</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>23/07/2020</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>23/07/2025</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1116,7 +1116,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>75272552</t>
+          <t>42898823</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TINEO</t>
+          <t>ASURSA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CARLOS EDUARDO</t>
+          <t>LEVI LEUMIN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>18/04/2004</t>
+          <t>05/01/1985</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>76305763</t>
+          <t>94573664</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>PICHUCA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AIXA FLOR</t>
+          <t>KIYOMI KASHIRI</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1203,21 +1203,21 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>21/08/2003</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1242,22 +1242,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>70934547</t>
+          <t>75272552</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CANDIA</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ALIAGA</t>
+          <t>TINEO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>RINAT BRIAN</t>
+          <t>CARLOS EDUARDO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1266,16 +1266,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>25/06/1992</t>
+          <t>18/04/2004</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1305,40 +1305,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>47406836</t>
+          <t>76305763</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CANO</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MOISES LEOCADIO</t>
+          <t>AIXA FLOR</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>23/10/1992</t>
+          <t>21/08/2003</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>29/05/2024</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1368,40 +1368,40 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>77453508</t>
+          <t>70934547</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t>CANDIA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BENITO</t>
+          <t>ALIAGA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>JAMILETH MISHELLE</t>
+          <t>RINAT BRIAN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>13/12/2011</t>
+          <t>25/06/1992</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>30/07/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,40 +1431,40 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>78629398</t>
+          <t>47406836</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t>CANO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BENITO</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VALERIE AMANDA</t>
+          <t>MOISES LEOCADIO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>21/05/2014</t>
+          <t>23/10/1992</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>30/07/2025</t>
+          <t>29/05/2024</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1494,22 +1494,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>92728182</t>
+          <t>44345957</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t>CASAS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BENITO</t>
+          <t>ANDAMAYO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SALOME LUZMILA</t>
+          <t>FIORELA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1518,21 +1518,21 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>27/01/2022</t>
+          <t>20/05/1987</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>30/07/2025</t>
+          <t>04/04/2025</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1557,40 +1557,40 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>44345957</t>
+          <t>71248100</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CASAS</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ANDAMAYO</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FIORELA</t>
+          <t>ROGER ISMAEL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20/05/1987</t>
+          <t>11/01/2005</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>04/04/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1620,45 +1620,45 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>71248100</t>
+          <t>93396934</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>CCENTE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ROGER ISMAEL</t>
+          <t>XIMENA MONSERRATH</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>11/01/2005</t>
+          <t>20/05/2023</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>22/07/2024</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1683,22 +1683,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>93396934</t>
+          <t>20983917</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CCENTE</t>
+          <t>CENTENO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SEBASTIAN</t>
+          <t>DE GARCIA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>XIMENA MONSERRATH</t>
+          <t>LUCIA ROSALIA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1707,21 +1707,21 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20/05/2023</t>
+          <t>21/10/1959</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>22/07/2024</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2061,22 +2061,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>04651057</t>
+          <t>92509938</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>COAPAZA</t>
+          <t>CLEMENTE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MAMANI</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SAMUEL</t>
+          <t>ANGEL SMITH</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2085,21 +2085,21 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>08/11/1975</t>
+          <t>26/08/2021</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>29/12/2025</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2124,40 +2124,40 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>21002105</t>
+          <t>04651057</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>COAPAZA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CORDOVA</t>
+          <t>MAMANI</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ENNA</t>
+          <t>SAMUEL</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>25/09/1960</t>
+          <t>08/11/1975</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>29/12/2025</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2187,22 +2187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>76264175</t>
+          <t>21002105</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CUTIMANCO</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>QUINTANA</t>
+          <t>CORDOVA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ROCXETT ALTAMIRA</t>
+          <t>ENNA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2211,16 +2211,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>21/01/1998</t>
+          <t>25/09/1960</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2250,40 +2250,40 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>73998397</t>
+          <t>76264175</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DAVILA</t>
+          <t>CUTIMANCO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SOVERO</t>
+          <t>QUINTANA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>YORDAN EDUARDO</t>
+          <t>ROCXETT ALTAMIRA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>07/12/1994</t>
+          <t>21/01/1998</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2313,35 +2313,35 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>92414136</t>
+          <t>94578369</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BERROCAL</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ISRAEL SAMUEL</t>
+          <t>ISABEL LEONOR</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>21/06/2021</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2376,22 +2376,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>75276735</t>
+          <t>73998397</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CANCHANYA</t>
+          <t>SOVERO</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CARLOS DANIEL</t>
+          <t>YORDAN EDUARDO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2400,16 +2400,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>14/04/2004</t>
+          <t>07/12/1994</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2439,22 +2439,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09738403</t>
+          <t>92414136</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BALBUENA</t>
+          <t>BERROCAL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AYLE</t>
+          <t>ISRAEL SAMUEL</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>26/10/1970</t>
+          <t>21/06/2021</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2502,35 +2502,35 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>76550309</t>
+          <t>75276735</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ESCALANTE</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CURO</t>
+          <t>CANCHANYA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NAYDA</t>
+          <t>CARLOS DANIEL</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20/06/1999</t>
+          <t>14/04/2004</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2565,22 +2565,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>82017126</t>
+          <t>09738403</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ESCOBAR</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CHANQUETE</t>
+          <t>BALBUENA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>YINO LISANDRO</t>
+          <t>AYLE</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>25/07/2022</t>
+          <t>26/10/1970</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2628,22 +2628,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>76325298</t>
+          <t>94567853</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ESPINAL</t>
+          <t>DOMINGUILLO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>ANTONIO</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MARIANELA KELY LEONELA</t>
+          <t>ROSELY</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2652,21 +2652,21 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>23/07/1998</t>
+          <t>03/03/2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2691,45 +2691,45 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>92269897</t>
+          <t>76550309</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ESQUIVEL</t>
+          <t>ESCALANTE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CAMACLLANQUI</t>
+          <t>CURO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>KEYSON THAYWA</t>
+          <t>NAYDA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>13/03/2021</t>
+          <t>20/06/1999</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2754,22 +2754,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>45265629</t>
+          <t>82017126</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EVANGELISTA</t>
+          <t>ESCOBAR</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GILVONIO</t>
+          <t>CHANQUETE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LEVI ADAN</t>
+          <t>YINO LISANDRO</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2778,21 +2778,21 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>22/06/1988</t>
+          <t>25/07/2022</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2817,22 +2817,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>94286708</t>
+          <t>76325298</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>ESPINAL</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PAUCARCAJA</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>EMMA</t>
+          <t>MARIANELA KELY LEONELA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>23/07/1998</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2880,45 +2880,45 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>75669769</t>
+          <t>92269897</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GALVEZ</t>
+          <t>ESQUIVEL</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PROA</t>
+          <t>CAMACLLANQUI</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>YENY NOEMI</t>
+          <t>KEYSON THAYWA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20/10/2002</t>
+          <t>13/03/2021</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>18/02/2025</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2943,40 +2943,40 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>60948568</t>
+          <t>45265629</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>EVANGELISTA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CENTENO</t>
+          <t>GILVONIO</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>JACKELYN LAURA</t>
+          <t>LEVI ADAN</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>28/08/2006</t>
+          <t>22/06/1988</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>03/09/2024</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3006,22 +3006,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>92144771</t>
+          <t>94286708</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MARAVI</t>
+          <t>PAUCARCAJA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DARA BERENICE</t>
+          <t>EMMA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3030,11 +3030,11 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>29/07/2020</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>29/07/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3069,35 +3069,35 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>61444783</t>
+          <t>75669769</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GAVINO</t>
+          <t>GALVEZ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MAGALLANES</t>
+          <t>PROA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>PAOLO SAMIR</t>
+          <t>YENY NOEMI</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>01/02/2008</t>
+          <t>20/10/2002</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>18/02/2025</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3132,45 +3132,45 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>80060427</t>
+          <t>92144771</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GILVONIO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LLIHUA</t>
+          <t>MARAVI</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>MAXIMILIANO</t>
+          <t>DARA BERENICE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>27/11/1978</t>
+          <t>29/07/2020</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>20/08/2024</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3195,35 +3195,35 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>61256308</t>
+          <t>61444783</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>GAVINO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ASPAJO</t>
+          <t>MAGALLANES</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MARIANA RUBI</t>
+          <t>PAOLO SAMIR</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>14/12/2007</t>
+          <t>01/02/2008</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>29/12/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3258,35 +3258,35 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>70811963</t>
+          <t>80060427</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>GILVONIO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>QUINTANILLA</t>
+          <t>LLIHUA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MIRELLA CHESSIRA</t>
+          <t>MAXIMILIANO</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>07/09/1995</t>
+          <t>27/11/1978</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>11/02/2025</t>
+          <t>20/08/2024</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3321,40 +3321,40 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>92034282</t>
+          <t>61256308</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GUSMAN</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>ASPAJO</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>BERAD JHEBAD</t>
+          <t>MARIANA RUBI</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>26/09/2020</t>
+          <t>14/12/2007</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>29/12/2025</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3384,22 +3384,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>82364968</t>
+          <t>70811963</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>QUINTANILLA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>YANELA</t>
+          <t>MIRELLA CHESSIRA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3408,21 +3408,21 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>08/06/2021</t>
+          <t>07/09/1995</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3447,22 +3447,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>74069430</t>
+          <t>92034282</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>GUSMAN</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CRISTHIAN MOISES</t>
+          <t>BERAD JHEBAD</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3471,16 +3471,16 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>02/04/1997</t>
+          <t>26/09/2020</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3510,35 +3510,35 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>92118592</t>
+          <t>82364968</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LIMAYMANTA</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CARLOS SAID</t>
+          <t>YANELA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>19/11/2020</t>
+          <t>08/06/2021</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3573,22 +3573,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>94605928</t>
+          <t>74069430</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HUAMANI</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CULLANCO</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>GHENDY KELLERMAN</t>
+          <t>CRISTHIAN MOISES</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3597,21 +3597,21 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>02/04/1997</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3636,22 +3636,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>71072200</t>
+          <t>92118592</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HUAMANI</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>YULGO</t>
+          <t>LIMAYMANTA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>IVAN</t>
+          <t>CARLOS SAID</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3660,21 +3660,21 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>03/02/1991</t>
+          <t>19/11/2020</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3699,22 +3699,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>91950176</t>
+          <t>94605928</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HUAMANTINCO</t>
+          <t>HUAMANI</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>VENTURO</t>
+          <t>CULLANCO</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>DILAN AXEL</t>
+          <t>GHENDY KELLERMAN</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3723,11 +3723,11 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>29/07/2020</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>29/07/2025</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3762,35 +3762,35 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>72120175</t>
+          <t>71072200</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>HUERTA</t>
+          <t>HUAMANI</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HUAYTAN</t>
+          <t>YULGO</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CATIVEL</t>
+          <t>IVAN</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>15/12/1994</t>
+          <t>03/02/1991</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3825,35 +3825,35 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>92270389</t>
+          <t>91950176</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JACOBO</t>
+          <t>HUAMANTINCO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CELESTINO</t>
+          <t>VENTURO</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>YALESSY JASU</t>
+          <t>DILAN AXEL</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>13/03/2021</t>
+          <t>29/07/2020</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3888,40 +3888,40 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>77505517</t>
+          <t>72120175</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JON</t>
+          <t>HUERTA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>HUAYTAN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>FRANK ANTONIO</t>
+          <t>CATIVEL</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>11/04/2006</t>
+          <t>15/12/1994</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>03/09/2025</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3951,35 +3951,35 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>93942843</t>
+          <t>92270389</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>JACOBO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SHIAMPA</t>
+          <t>CELESTINO</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EYLER</t>
+          <t>YALESSY JASU</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>13/03/2021</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4014,35 +4014,35 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>91941385</t>
+          <t>93942843</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LAZO</t>
+          <t>JOSE</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GARMA</t>
+          <t>SHIAMPA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ELEN MARIETTDUVITHA</t>
+          <t>EYLER</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>23/07/2020</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>23/07/2025</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4077,7 +4077,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>92327614</t>
+          <t>91941385</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4087,25 +4087,25 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>GARMA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ALHY ISMAEL</t>
+          <t>ELEN MARIETTDUVITHA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>23/04/2021</t>
+          <t>23/07/2020</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>23/07/2025</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4140,7 +4140,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>90647340</t>
+          <t>92327614</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TICLLAS</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>JHOEL JHENDERS</t>
+          <t>ALHY ISMAEL</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4164,11 +4164,11 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>24/02/2018</t>
+          <t>23/04/2021</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4203,22 +4203,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10751783</t>
+          <t>90647340</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LEVANO</t>
+          <t>LAZO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>TICLLAS</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>RAUL CARLOS</t>
+          <t>JHOEL JHENDERS</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4227,16 +4227,16 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>10/02/1978</t>
+          <t>24/02/2018</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4266,22 +4266,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>41680437</t>
+          <t>10751783</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LINO</t>
+          <t>LEVANO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ESPIRITU</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>TITO WALTER</t>
+          <t>RAUL CARLOS</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4290,11 +4290,11 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>06/02/1979</t>
+          <t>10/02/1978</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4329,22 +4329,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>73173972</t>
+          <t>41680437</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LLANCE</t>
+          <t>LINO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>ESPIRITU</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>JHEAN JHONATAN</t>
+          <t>TITO WALTER</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4353,16 +4353,16 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>13/12/1997</t>
+          <t>06/02/1979</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4392,22 +4392,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>74173759</t>
+          <t>73173972</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MAHUANCA</t>
+          <t>LLANCE</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CHIRICENTE</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>HERLY ROEL</t>
+          <t>JHEAN JHONATAN</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4416,11 +4416,11 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>17/08/2001</t>
+          <t>13/12/1997</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4455,45 +4455,45 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>92464757</t>
+          <t>74173759</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>MAHUANCA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SANTA CRUZ</t>
+          <t>CHIRICENTE</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>YELITZA</t>
+          <t>HERLY ROEL</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>24/06/2021</t>
+          <t>17/08/2001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4518,22 +4518,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>77159359</t>
+          <t>92464757</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MARIN</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>SANTA CRUZ</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>MEYLIN MELIZA</t>
+          <t>YELITZA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4542,21 +4542,21 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>03/03/2006</t>
+          <t>24/06/2021</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4581,45 +4581,45 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>92420427</t>
+          <t>77159359</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MAYTA</t>
+          <t>MARIN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LIAN MOISES</t>
+          <t>MEYLIN MELIZA</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>25/06/2021</t>
+          <t>03/03/2006</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4644,45 +4644,45 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>73198204</t>
+          <t>92420427</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>MAYTA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SHELVY CELYM</t>
+          <t>LIAN MOISES</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>30/06/1998</t>
+          <t>25/06/2021</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4707,35 +4707,35 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>73440461</t>
+          <t>73198204</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BARBARON</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>KINLIMBERG RUSSO</t>
+          <t>SHELVY CELYM</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>22/08/2000</t>
+          <t>30/06/1998</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4770,40 +4770,40 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>92152266</t>
+          <t>73440461</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AMES</t>
+          <t>BARBARON</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ALESSANDRA VRADESHCA</t>
+          <t>KINLIMBERG RUSSO</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>13/12/2020</t>
+          <t>22/08/2000</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>29/12/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4833,22 +4833,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>93876723</t>
+          <t>92152266</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MILAN</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>AMES</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SILVIA JIMENA</t>
+          <t>ALESSANDRA VRADESHCA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4857,11 +4857,11 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>08/06/2019</t>
+          <t>13/12/2020</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>31/07/2024</t>
+          <t>29/12/2025</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4896,22 +4896,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>76417696</t>
+          <t>93876723</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MISARAYME</t>
+          <t>MILAN</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>QUIÑONEZ</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>BRENDA EVELYN</t>
+          <t>SILVIA JIMENA</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4920,16 +4920,16 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>18/11/2002</t>
+          <t>08/06/2019</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>31/07/2024</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4959,35 +4959,35 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>60185820</t>
+          <t>76417696</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MISHICURI</t>
+          <t>MISARAYME</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ALEGRIA</t>
+          <t>QUIÑONEZ</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>RIVALDO</t>
+          <t>BRENDA EVELYN</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>19/01/2004</t>
+          <t>18/11/2002</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5022,22 +5022,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>90695093</t>
+          <t>60185820</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MORI</t>
+          <t>MISHICURI</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PAQUI</t>
+          <t>ALEGRIA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ISAI IGNACIO</t>
+          <t>RIVALDO</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5046,16 +5046,16 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>17/03/2018</t>
+          <t>19/01/2004</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5085,22 +5085,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>91912222</t>
+          <t>90695093</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>MORI</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SORIA</t>
+          <t>PAQUI</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>MILMER</t>
+          <t>ISAI IGNACIO</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5109,11 +5109,11 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>30/06/2020</t>
+          <t>17/03/2018</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5148,7 +5148,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>91660823</t>
+          <t>91912222</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>SORIA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>GHAEL IYAN ALDEMAR</t>
+          <t>MILMER</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>30/06/2020</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5211,22 +5211,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>77659342</t>
+          <t>91660823</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CHANQUETE</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>JUNIOR PEPE</t>
+          <t>GHAEL IYAN ALDEMAR</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5235,16 +5235,16 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>17/09/2003</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5274,7 +5274,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>72302311</t>
+          <t>77659342</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5284,30 +5284,30 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MAÑAHUIRI</t>
+          <t>CHANQUETE</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>JUANA</t>
+          <t>JUNIOR PEPE</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>24/05/1995</t>
+          <t>17/09/2003</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>02/05/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5337,40 +5337,40 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>92441541</t>
+          <t>72302311</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NINAHUANCA</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>OSCANOA</t>
+          <t>MAÑAHUIRI</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LUIS MIGUEL</t>
+          <t>JUANA</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>09/07/2021</t>
+          <t>24/05/1995</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>02/05/2025</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5400,22 +5400,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>47617480</t>
+          <t>92441541</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>OCHICUA</t>
+          <t>NINAHUANCA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BETTER</t>
+          <t>OSCANOA</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>JHYN LUIS</t>
+          <t>LUIS MIGUEL</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5424,16 +5424,16 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>24/10/1991</t>
+          <t>09/07/2021</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5463,22 +5463,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>75957326</t>
+          <t>47617480</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>OCHICUA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TINTA</t>
+          <t>BETTER</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>OSWALDO JAHIRO</t>
+          <t>JHYN LUIS</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5487,16 +5487,16 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>08/05/1999</t>
+          <t>24/10/1991</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5526,22 +5526,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>48345322</t>
+          <t>75957326</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ORELLANA</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MENESES</t>
+          <t>TINTA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>JAIME</t>
+          <t>OSWALDO JAHIRO</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5550,16 +5550,16 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>25/07/1993</t>
+          <t>08/05/1999</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5589,7 +5589,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>73071269</t>
+          <t>48345322</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SUCUITANA</t>
+          <t>MENESES</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LUIS ALFREDO</t>
+          <t>JAIME</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5613,11 +5613,11 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>28/09/1996</t>
+          <t>25/07/1993</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5652,35 +5652,35 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>74841035</t>
+          <t>73071269</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ORTEGA</t>
+          <t>ORELLANA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>SUCUITANA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>TATYANA AFRODITA</t>
+          <t>LUIS ALFREDO</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>01/08/1994</t>
+          <t>28/09/1996</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5715,22 +5715,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>63418421</t>
+          <t>92509001</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>OROSCO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>JANAMPA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>SEBASTIAN</t>
+          <t>NOE IMER</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5739,11 +5739,11 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>08/05/2015</t>
+          <t>26/08/2021</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>03/09/2024</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5778,22 +5778,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>92061264</t>
+          <t>74841035</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>OTAROLA</t>
+          <t>ORTEGA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TATYANA AFRODITA</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5802,16 +5802,16 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>14/10/2020</t>
+          <t>01/08/1994</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5841,22 +5841,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>81832366</t>
+          <t>63418421</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PABLO</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SANTONINO</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ELI JOEL</t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5865,11 +5865,11 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>02/11/2020</t>
+          <t>08/05/2015</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>03/09/2024</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5904,40 +5904,40 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>73863007</t>
+          <t>92061264</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PAICO</t>
+          <t>OTAROLA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ALEXANDRO</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>06/05/2002</t>
+          <t>14/10/2020</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5967,55 +5967,55 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>94477359</t>
+          <t>81832366</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PAITAN</t>
+          <t>PABLO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GASPAR</t>
+          <t>SANTONINO</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>MIA YAMILETH</t>
+          <t>ELI JOEL</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
+          <t>02/11/2020</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t>12/12/2025</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>16/12/2025</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6030,45 +6030,45 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>92118196</t>
+          <t>73863007</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PALMA</t>
+          <t>PAICO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>REATEGUI</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ALESSIA DANAE</t>
+          <t>ALEXANDRO</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>19/11/2020</t>
+          <t>06/05/2002</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6093,22 +6093,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>74690615</t>
+          <t>94477359</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PAMPAS</t>
+          <t>PAITAN</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>GASPAR</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ROXANA</t>
+          <t>MIA YAMILETH</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6117,21 +6117,21 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>22/02/1998</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6156,22 +6156,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>21011537</t>
+          <t>92118196</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PARDO</t>
+          <t>PALMA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ANTONIO</t>
+          <t>REATEGUI</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>CLAUDIA</t>
+          <t>ALESSIA DANAE</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6180,21 +6180,21 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20/03/1961</t>
+          <t>19/11/2020</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6219,40 +6219,40 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>76728774</t>
+          <t>74690615</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PARIACHI</t>
+          <t>PAMPAS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CUÑIVO</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>GESER RONALD</t>
+          <t>ROXANA</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>15/03/1996</t>
+          <t>22/02/1998</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6282,35 +6282,35 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>91855829</t>
+          <t>92510301</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PARIACHI</t>
+          <t>PAQUI</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>LAZARO</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VALENTIN JUNIOR</t>
+          <t>CARMENCITA YASURI</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>16/05/2020</t>
+          <t>26/08/2021</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6345,40 +6345,40 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>46350087</t>
+          <t>21011537</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>PARDO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>ANTONIO</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LISMAN CARLOS</t>
+          <t>CLAUDIA</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>31/05/1990</t>
+          <t>20/03/1961</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>29/12/2025</t>
+          <t>19/08/2025</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6408,45 +6408,45 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>91949940</t>
+          <t>76728774</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>PARIACHI</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SOBRINO</t>
+          <t>CUÑIVO</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>KATLEYA ZOE</t>
+          <t>GESER RONALD</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>29/07/2020</t>
+          <t>15/03/1996</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>29/07/2025</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6471,22 +6471,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>91996112</t>
+          <t>91855829</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>PARIACHI</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>UMPIQUIRI</t>
+          <t>LAZARO</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>JACK TEDDY</t>
+          <t>VALENTIN JUNIOR</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>29/07/2020</t>
+          <t>16/05/2020</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>29/07/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6534,35 +6534,35 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>92061695</t>
+          <t>92483488</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>QUINTANA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>UNSIHUAY</t>
+          <t>ARCO</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>BRIANA ARLETH</t>
+          <t>GAEL PATRICK</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>14/10/2020</t>
+          <t>08/08/2021</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6597,22 +6597,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>94647520</t>
+          <t>46350087</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ARCA</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ZAEL SAMIR</t>
+          <t>LISMAN CARLOS</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6621,21 +6621,21 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>31/05/1990</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>29/12/2025</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6660,22 +6660,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>78554669</t>
+          <t>91949940</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ORIHUELA</t>
+          <t>SOBRINO</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>BRIANA DANIELA</t>
+          <t>KATLEYA ZOE</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6684,21 +6684,21 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>06/04/2014</t>
+          <t>29/07/2020</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6723,22 +6723,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>75285464</t>
+          <t>91996112</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MAÑUICO</t>
+          <t>UMPIQUIRI</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>JHON ANTONY</t>
+          <t>JACK TEDDY</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6747,21 +6747,21 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>01/04/1998</t>
+          <t>29/07/2020</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6786,35 +6786,35 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>92104257</t>
+          <t>90653705</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>RASHUAMAN</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FABIAN</t>
+          <t>VILLALVA</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>UZIEL DANIEL</t>
+          <t>DANNA DALUSKA</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>10/11/2020</t>
+          <t>27/02/2018</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6849,22 +6849,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>92474195</t>
+          <t>92061695</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>RAYMUNDO</t>
+          <t>QUINTANA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>UNSIHUAY</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ALESSIA ZOE</t>
+          <t>BRIANA ARLETH</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6873,11 +6873,11 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>02/08/2021</t>
+          <t>14/10/2020</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6912,35 +6912,35 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>92460080</t>
+          <t>94647520</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>REMUZGO</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>PANCHO</t>
+          <t>ARCA</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>MARY CARMEN</t>
+          <t>ZAEL SAMIR</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>22/07/2021</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6975,22 +6975,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>78548631</t>
+          <t>63267186</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>DELGADO</t>
+          <t>TUESTA</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>JOHANA CLAUDINA</t>
+          <t>YAMELI YURICO</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6999,11 +6999,11 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>12/01/2003</t>
+          <t>25/07/2004</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7038,22 +7038,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>92459078</t>
+          <t>78554669</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>ORIHUELA</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>BRIANA KELSI</t>
+          <t>BRIANA DANIELA</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -7062,21 +7062,21 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>21/07/2021</t>
+          <t>06/04/2014</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7101,22 +7101,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>60786771</t>
+          <t>92510667</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>RODRIGO</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>BRUNO BRAYAN</t>
+          <t>LIAN JAIRO</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7125,21 +7125,21 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>07/06/2006</t>
+          <t>26/08/2021</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>18/06/2024</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7164,22 +7164,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>41786424</t>
+          <t>75285464</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ARANDA</t>
+          <t>MAÑUICO</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>HELMER LEONIDAS</t>
+          <t>JHON ANTONY</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7188,16 +7188,16 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>04/05/1982</t>
+          <t>01/04/1998</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>10/07/2024</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7227,22 +7227,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>72016831</t>
+          <t>92104257</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>RASHUAMAN</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BENDEZU</t>
+          <t>FABIAN</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>CESAR SAMUEL</t>
+          <t>UZIEL DANIEL</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7251,21 +7251,21 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>31/12/1999</t>
+          <t>10/11/2020</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7290,22 +7290,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>92419021</t>
+          <t>92474195</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ROMANI</t>
+          <t>RAYMUNDO</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MENDIOLAZA</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ZOE ISABEL</t>
+          <t>ALESSIA ZOE</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>24/06/2021</t>
+          <t>02/08/2021</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7353,45 +7353,45 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>48121806</t>
+          <t>92460080</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t>REMUZGO</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>PANCHO</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>JOHN MIJAEL</t>
+          <t>MARY CARMEN</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>18/02/1988</t>
+          <t>22/07/2021</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7416,22 +7416,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>94438245</t>
+          <t>78548631</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ROSPIGLIOSI</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MAYHUANTI</t>
+          <t>DELGADO</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>DANNAE ARIANA</t>
+          <t>JOHANA CLAUDINA</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7440,21 +7440,21 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>12/01/2003</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7479,22 +7479,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>92269981</t>
+          <t>92459078</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SAENZ</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>PAUCAR</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NAIRA ANALI</t>
+          <t>BRIANA KELSI</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>13/03/2021</t>
+          <t>21/07/2021</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7542,45 +7542,45 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>92459642</t>
+          <t>60786771</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SALAS</t>
+          <t>RODRIGO</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>LARA</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ASHLEY JHOSABET</t>
+          <t>BRUNO BRAYAN</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>21/07/2021</t>
+          <t>07/06/2006</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>18/06/2024</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7605,22 +7605,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>47943181</t>
+          <t>41786424</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SALDAÑA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>ARANDA</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>JHOA CHRISTIAN</t>
+          <t>HELMER LEONIDAS</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7629,11 +7629,11 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>02/08/1993</t>
+          <t>04/05/1982</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>10/07/2024</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7668,22 +7668,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>92259920</t>
+          <t>72016831</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BARRETO</t>
+          <t>BENDEZU</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>GAEL JAIME</t>
+          <t>CESAR SAMUEL</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7692,16 +7692,16 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>06/03/2021</t>
+          <t>31/12/1999</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7731,22 +7731,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>91950188</t>
+          <t>92419021</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SHUMPATI</t>
+          <t>ROMANI</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>MENDIOLAZA</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>JHASMIN HEYRA</t>
+          <t>ZOE ISABEL</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7755,11 +7755,11 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>29/07/2020</t>
+          <t>24/06/2021</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>29/07/2025</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7794,22 +7794,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>92383249</t>
+          <t>48121806</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SIERRA</t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>PAMPAS</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>JAIRO SAMIR</t>
+          <t>JOHN MIJAEL</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7818,16 +7818,16 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>30/05/2021</t>
+          <t>18/02/1988</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7857,22 +7857,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>94303923</t>
+          <t>94438245</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SOLIS</t>
+          <t>ROSPIGLIOSI</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>MAYHUANTI</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>KARELIZ SARAY</t>
+          <t>DANNAE ARIANA</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>05/07/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7920,22 +7920,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>92267094</t>
+          <t>60220228</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>YANANCURI</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>DYLAN PERCY</t>
+          <t>ERIK EDWIN</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7944,16 +7944,16 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>11/03/2021</t>
+          <t>06/04/2001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7983,22 +7983,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>81757730</t>
+          <t>92269981</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SUAZO</t>
+          <t>SAENZ</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>PAUCAR</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>CAMILA DOMINGA</t>
+          <t>NAIRA ANALI</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8007,11 +8007,11 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>23/07/2020</t>
+          <t>13/03/2021</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>23/07/2025</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8046,22 +8046,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>92211363</t>
+          <t>92459642</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SURICHAQUI</t>
+          <t>SALAS</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>GAUGA</t>
+          <t>LARA</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ESTRELLA SALOME</t>
+          <t>ASHLEY JHOSABET</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>28/01/2021</t>
+          <t>21/07/2021</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8109,22 +8109,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>92394996</t>
+          <t>92509183</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TAIPE</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SEDANO</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>HANSEL YENSEI</t>
+          <t>CAMILO STELLO ENRRIQUE</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>08/06/2021</t>
+          <t>26/08/2021</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8172,40 +8172,40 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>74974093</t>
+          <t>47943181</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TAQUIRE</t>
+          <t>SALDAÑA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>EMILY YASSDELY</t>
+          <t>JHOA CHRISTIAN</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>04/05/1999</t>
+          <t>02/08/1993</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8235,27 +8235,27 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>92457610</t>
+          <t>92259920</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TEJADA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CHIRISENTE</t>
+          <t>BARRETO</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NIRLET YELIXA</t>
+          <t>GAEL JAIME</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>21/07/2021</t>
+          <t>06/03/2021</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8298,22 +8298,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>92417110</t>
+          <t>91950188</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TELLO</t>
+          <t>SHUMPATI</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>KENDRA EDURNE</t>
+          <t>JHASMIN HEYRA</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8322,11 +8322,11 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>22/06/2021</t>
+          <t>29/07/2020</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8361,40 +8361,40 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>73780756</t>
+          <t>92383249</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>SIERRA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>TANGOA</t>
+          <t>PAMPAS</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>MARIANELA</t>
+          <t>JAIRO SAMIR</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>18/03/2004</t>
+          <t>30/05/2021</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8424,22 +8424,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>78532814</t>
+          <t>94303923</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>SOLIS</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MALPARTIDA</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ROSE KIARA</t>
+          <t>KARELIZ SARAY</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8448,21 +8448,21 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>03/04/2014</t>
+          <t>05/07/2025</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>11/02/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8487,22 +8487,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>92572906</t>
+          <t>92267094</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>PINEDO</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ARTURO ACXEL</t>
+          <t>DYLAN PERCY</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>23/01/2021</t>
+          <t>11/03/2021</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8550,22 +8550,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>44863817</t>
+          <t>81757730</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TOVAR</t>
+          <t>SUAZO</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CHIHUAN</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>SOLEDAD</t>
+          <t>CAMILA DOMINGA</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8574,16 +8574,16 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>21/08/1982</t>
+          <t>23/07/2020</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>06/07/2013</t>
+          <t>23/07/2025</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8613,35 +8613,35 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>92118073</t>
+          <t>92211363</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>UNCHUPAICO</t>
+          <t>SURICHAQUI</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>GAUGA</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>GAEL SEBASTIAN</t>
+          <t>ESTRELLA SALOME</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>19/11/2020</t>
+          <t>28/01/2021</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8676,45 +8676,45 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>77483796</t>
+          <t>92394996</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>VALERO</t>
+          <t>TAIPE</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>TOVAR</t>
+          <t>SEDANO</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>JAQUI YADITH</t>
+          <t>HANSEL YENSEI</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>06/03/2004</t>
+          <t>08/06/2021</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>VULNERABILIDAD SANITARIA - DISCAPACIDAD SEVERA (DS Nº 002-2020-SA)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>06/07/2013</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8739,45 +8739,45 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>62207706</t>
+          <t>74974093</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>VALERO</t>
+          <t>TAQUIRE</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TOVAR</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>EDINSON</t>
+          <t>EMILY YASSDELY</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>11/08/2010</t>
+          <t>04/05/1999</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>14/03/2019</t>
+          <t>11/02/2026</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8802,35 +8802,35 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>92118606</t>
+          <t>92457610</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>VALERO</t>
+          <t>TEJADA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>CHIRISENTE</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>PATRICK SMITTH</t>
+          <t>NIRLET YELIXA</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>19/11/2020</t>
+          <t>21/07/2021</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8865,27 +8865,27 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>92182206</t>
+          <t>92417110</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>TELLO</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>PUENTE</t>
+          <t>VELIZ</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>DARWIN ANTONIO</t>
+          <t>KENDRA EDURNE</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -8893,7 +8893,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>05/01/2021</t>
+          <t>22/06/2021</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8928,22 +8928,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>75279953</t>
+          <t>73780756</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SALAS</t>
+          <t>TANGOA</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>MARA KRISTEL</t>
+          <t>MARIANELA</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8952,11 +8952,11 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>04/10/2005</t>
+          <t>18/03/2004</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8991,22 +8991,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>41172450</t>
+          <t>78532814</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>VELASQUEZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>MALPARTIDA</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>CARMEN ROSA</t>
+          <t>ROSE KIARA</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -9015,16 +9015,16 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>02/12/1981</t>
+          <t>03/04/2014</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9054,22 +9054,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>92421803</t>
+          <t>92572906</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>BERNARDO</t>
+          <t>PINEDO</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>PEDRO ARTURO</t>
+          <t>ARTURO ACXEL</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>25/06/2021</t>
+          <t>23/01/2021</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -9117,22 +9117,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>92299052</t>
+          <t>44863817</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>VERA</t>
+          <t>TOVAR</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>CHIHUAN</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>KATALLEA ASUMI</t>
+          <t>SOLEDAD</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -9141,21 +9141,21 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>03/04/2021</t>
+          <t>21/08/1982</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>06/07/2013</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -9180,45 +9180,45 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>72877156</t>
+          <t>92118073</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>YUPANQUI</t>
+          <t>UNCHUPAICO</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>HUALLULLO</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>GLEYDI DANEY</t>
+          <t>GAEL SEBASTIAN</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20/05/1993</t>
+          <t>19/11/2020</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -9243,63 +9243,693 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
+          <t>77483796</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>VALERO</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>TOVAR</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>JAQUI YADITH</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>22</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>06/03/2004</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>3.JOVEN</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>VULNERABILIDAD SANITARIA - DISCAPACIDAD SEVERA (DS Nº 002-2020-SA)</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>06/07/2013</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M141" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>62207706</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>VALERO</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>TOVAR</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>EDINSON</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>16</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>11/08/2010</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>2.ADOLESCENTE</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>14/03/2019</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M142" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>92118606</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>VALERO</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>VASQUEZ</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>PATRICK SMITTH</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>6</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>19/11/2020</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>19/11/2025</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M143" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>92182206</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>VASQUEZ</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>PUENTE</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>DARWIN ANTONIO</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>5</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>05/01/2021</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>13/01/2026</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M144" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>75279953</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>VASQUEZ</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>SALAS</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>MARA KRISTEL</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>21</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>04/10/2005</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>3.JOVEN</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>06/01/2025</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M145" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>74401598</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>VEGA</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>DE LA CRUZ</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>LIZ ALESSANDRA</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>25</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>07/04/2001</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>3.JOVEN</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M146" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>41172450</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>APOLINARIO</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>CARMEN ROSA</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>45</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>02/12/1981</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>4.ADULTO</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>05/04/2025</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M147" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>92421803</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>VELIZ</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>BERNARDO</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>PEDRO ARTURO</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>5</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>25/06/2021</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M148" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>92299052</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>VERA</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>KATALLEA ASUMI</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>5</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>03/04/2021</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M149" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>40405181</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>YAURI</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>ORELLANA</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>EVELYN KATYUSCA</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>46</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>15/01/1980</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>4.ADULTO</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M150" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
           <t>81932339</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B151" t="inlineStr">
         <is>
           <t>ZACARIAS</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="C151" t="inlineStr">
         <is>
           <t>ASENCIO</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>CELESTE RUTH</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="E151" t="inlineStr">
         <is>
           <t>Femenino</t>
         </is>
       </c>
-      <c r="F141" t="n">
+      <c r="F151" t="n">
         <v>5</v>
       </c>
-      <c r="G141" t="inlineStr">
+      <c r="G151" t="inlineStr">
         <is>
           <t>22/06/2021</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
+      <c r="H151" t="inlineStr">
         <is>
           <t>1.NIÑO</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
+      <c r="I151" t="inlineStr">
         <is>
           <t>AFILIACION PPDD</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>MAZAMARI</t>
-        </is>
-      </c>
-      <c r="M141" t="n">
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M151" t="n">
         <v>120604</v>
       </c>
     </row>
